--- a/方块 block/试炼和宝库.xlsx
+++ b/方块 block/试炼和宝库.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\方块 block\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD3F1CA-7676-4797-BC9A-694F47090AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079FDD40-3E0F-4011-8452-33555790057F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6290" yWindow="2760" windowWidth="16360" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="试炼" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="64">
   <si>
     <t>普通</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -284,6 +284,14 @@
   </si>
   <si>
     <t>最后，普通宝库0.25概率独有，不祥宝库0.75概率独有</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每盒的钥匙期望数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每盒的试炼期望次数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -700,7 +708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36.33203125" customWidth="1"/>
@@ -710,9 +718,10 @@
     <col min="7" max="7" width="13.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.08203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>51</v>
       </c>
@@ -740,8 +749,14 @@
       <c r="I1" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -774,8 +789,16 @@
         <f>1/G2</f>
         <v>1.1363636363636362</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <f>H2*1728</f>
+        <v>981.81818181818176</v>
+      </c>
+      <c r="K2">
+        <f>I2*1728</f>
+        <v>1963.6363636363635</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -808,8 +831,16 @@
         <f t="shared" ref="I3:I46" si="3">1/G3</f>
         <v>1.1363636363636362</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <f t="shared" ref="J3:J46" si="4">H3*1728</f>
+        <v>981.81818181818176</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K46" si="5">I3*1728</f>
+        <v>1963.6363636363635</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -842,8 +873,16 @@
         <f t="shared" si="3"/>
         <v>3.7878787878787876</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <f t="shared" si="4"/>
+        <v>3272.7272727272725</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="5"/>
+        <v>6545.454545454545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -876,8 +915,16 @@
         <f t="shared" si="3"/>
         <v>2.8409090909090908</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <f t="shared" si="4"/>
+        <v>2454.5454545454545</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="5"/>
+        <v>4909.090909090909</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -910,8 +957,16 @@
         <f t="shared" si="3"/>
         <v>3.0303030303030303</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <f t="shared" si="4"/>
+        <v>2618.181818181818</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="5"/>
+        <v>5236.363636363636</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -944,8 +999,16 @@
         <f t="shared" si="3"/>
         <v>1.8939393939393938</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <f t="shared" si="4"/>
+        <v>1636.3636363636363</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="5"/>
+        <v>3272.7272727272725</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
@@ -978,8 +1041,16 @@
         <f t="shared" si="3"/>
         <v>15.15151515151515</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <f t="shared" si="4"/>
+        <v>13090.90909090909</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="5"/>
+        <v>26181.81818181818</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -1012,8 +1083,16 @@
         <f t="shared" si="3"/>
         <v>5.0505050505050502</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <f t="shared" si="4"/>
+        <v>4363.6363636363631</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="5"/>
+        <v>8727.2727272727261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1046,8 +1125,16 @@
         <f t="shared" si="3"/>
         <v>11.363636363636363</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <f t="shared" si="4"/>
+        <v>9818.181818181818</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="5"/>
+        <v>19636.363636363636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1080,8 +1167,16 @@
         <f t="shared" si="3"/>
         <v>6.3888888888888884</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <f t="shared" si="4"/>
+        <v>5520</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="5"/>
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1099,7 +1194,7 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" ref="F12:F21" si="4">0.8*E12*(C12+D12)/2</f>
+        <f t="shared" ref="F12:F21" si="6">0.8*E12*(C12+D12)/2</f>
         <v>0.10434782608695653</v>
       </c>
       <c r="G12" s="1">
@@ -1114,8 +1209,16 @@
         <f t="shared" si="3"/>
         <v>19.166666666666664</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>16559.999999999996</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="5"/>
+        <v>33119.999999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -1133,7 +1236,7 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.10434782608695653</v>
       </c>
       <c r="G13" s="1">
@@ -1148,8 +1251,16 @@
         <f t="shared" si="3"/>
         <v>19.166666666666664</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>16559.999999999996</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="5"/>
+        <v>33119.999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1167,7 +1278,7 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.10434782608695653</v>
       </c>
       <c r="G14" s="1">
@@ -1182,8 +1293,16 @@
         <f t="shared" si="3"/>
         <v>19.166666666666664</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <f t="shared" si="4"/>
+        <v>16559.999999999996</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="5"/>
+        <v>33119.999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1201,7 +1320,7 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G15" s="1">
@@ -1216,8 +1335,16 @@
         <f t="shared" si="3"/>
         <v>28.75</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <f t="shared" si="4"/>
+        <v>24840</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="5"/>
+        <v>49680</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1235,7 +1362,7 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G16" s="1">
@@ -1250,8 +1377,16 @@
         <f t="shared" si="3"/>
         <v>28.75</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <f t="shared" si="4"/>
+        <v>24840</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="5"/>
+        <v>49680</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1269,7 +1404,7 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G17" s="1">
@@ -1284,8 +1419,16 @@
         <f t="shared" si="3"/>
         <v>28.75</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <f t="shared" si="4"/>
+        <v>24840</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="5"/>
+        <v>49680</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1303,7 +1446,7 @@
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="G18" s="1">
@@ -1318,8 +1461,16 @@
         <f t="shared" si="3"/>
         <v>57.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <f t="shared" si="4"/>
+        <v>49680</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="5"/>
+        <v>99360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -1337,7 +1488,7 @@
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="G19" s="1">
@@ -1352,8 +1503,16 @@
         <f t="shared" si="3"/>
         <v>57.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <f t="shared" si="4"/>
+        <v>49680</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="5"/>
+        <v>99360</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1371,7 +1530,7 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G20" s="1">
@@ -1386,8 +1545,16 @@
         <f t="shared" si="3"/>
         <v>28.75</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <f t="shared" si="4"/>
+        <v>24840</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="5"/>
+        <v>49680</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -1405,7 +1572,7 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G21" s="1">
@@ -1420,8 +1587,16 @@
         <f t="shared" si="3"/>
         <v>28.75</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <f t="shared" si="4"/>
+        <v>24840</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="5"/>
+        <v>49680</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -1454,8 +1629,16 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <f t="shared" si="4"/>
+        <v>20736</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="5"/>
+        <v>41472</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -1473,7 +1656,7 @@
         <v>0.25</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" ref="F23:F26" si="5">0.25*E23*(C23+D23)/2</f>
+        <f t="shared" ref="F23:F26" si="7">0.25*E23*(C23+D23)/2</f>
         <v>6.25E-2</v>
       </c>
       <c r="G23" s="1">
@@ -1488,8 +1671,16 @@
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <f t="shared" si="4"/>
+        <v>27648</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="5"/>
+        <v>55296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>2</v>
       </c>
@@ -1507,7 +1698,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="G24" s="1">
@@ -1522,8 +1713,16 @@
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <f t="shared" si="4"/>
+        <v>41472</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="5"/>
+        <v>82944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>2</v>
       </c>
@@ -1541,7 +1740,7 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="G25" s="1">
@@ -1556,8 +1755,16 @@
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <f t="shared" si="4"/>
+        <v>41472</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="5"/>
+        <v>82944</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -1575,7 +1782,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="G26" s="1">
@@ -1590,8 +1797,16 @@
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <f t="shared" si="4"/>
+        <v>82944</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="5"/>
+        <v>165888</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1624,8 +1839,16 @@
         <f t="shared" si="3"/>
         <v>22.72727272727273</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <f t="shared" si="4"/>
+        <v>11781.818181818182</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="5"/>
+        <v>39272.727272727279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1647,7 +1870,7 @@
         <v>3.5200000000000005</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" ref="G28:G46" si="6">F28*0.3</f>
+        <f t="shared" ref="G28:G46" si="8">F28*0.3</f>
         <v>1.056</v>
       </c>
       <c r="H28" s="1">
@@ -1658,8 +1881,16 @@
         <f t="shared" si="3"/>
         <v>0.94696969696969691</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <f t="shared" si="4"/>
+        <v>490.90909090909088</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="5"/>
+        <v>1636.3636363636363</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>3</v>
       </c>
@@ -1681,7 +1912,7 @@
         <v>5.8666666666666671</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.76</v>
       </c>
       <c r="H29" s="3">
@@ -1692,8 +1923,16 @@
         <f t="shared" si="3"/>
         <v>0.56818181818181823</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <f t="shared" si="4"/>
+        <v>294.5454545454545</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="5"/>
+        <v>981.81818181818187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1715,7 +1954,7 @@
         <v>5.1333333333333337</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.54</v>
       </c>
       <c r="H30" s="1">
@@ -1726,8 +1965,16 @@
         <f t="shared" si="3"/>
         <v>0.64935064935064934</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <f t="shared" si="4"/>
+        <v>336.6233766233766</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="5"/>
+        <v>1122.077922077922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>3</v>
       </c>
@@ -1749,7 +1996,7 @@
         <v>0.73333333333333339</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.22</v>
       </c>
       <c r="H31" s="3">
@@ -1760,8 +2007,16 @@
         <f t="shared" si="3"/>
         <v>4.5454545454545459</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <f t="shared" si="4"/>
+        <v>2356.363636363636</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="5"/>
+        <v>7854.545454545455</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1783,7 +2038,7 @@
         <v>0.1103448275862069</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.310344827586207E-2</v>
       </c>
       <c r="H32" s="1">
@@ -1794,8 +2049,16 @@
         <f t="shared" si="3"/>
         <v>30.208333333333332</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <f t="shared" si="4"/>
+        <v>15660</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="5"/>
+        <v>52200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1813,11 +2076,11 @@
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="F33" s="1">
-        <f t="shared" ref="F33:F41" si="7">0.8*E33*(C33+D33)/2</f>
+        <f t="shared" ref="F33:F41" si="9">0.8*E33*(C33+D33)/2</f>
         <v>5.5172413793103448E-2</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.6551724137931035E-2</v>
       </c>
       <c r="H33" s="1">
@@ -1828,8 +2091,16 @@
         <f t="shared" si="3"/>
         <v>60.416666666666664</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <f t="shared" si="4"/>
+        <v>31320</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1847,11 +2118,11 @@
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5.5172413793103448E-2</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.6551724137931035E-2</v>
       </c>
       <c r="H34" s="1">
@@ -1862,8 +2133,16 @@
         <f t="shared" si="3"/>
         <v>60.416666666666664</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <f t="shared" si="4"/>
+        <v>31320</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1881,11 +2160,11 @@
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="F35" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5.5172413793103448E-2</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.6551724137931035E-2</v>
       </c>
       <c r="H35" s="1">
@@ -1896,8 +2175,16 @@
         <f t="shared" si="3"/>
         <v>60.416666666666664</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <f t="shared" si="4"/>
+        <v>31320</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="5"/>
+        <v>104400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1915,11 +2202,11 @@
         <v>0.10344827586206896</v>
       </c>
       <c r="F36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>8.2758620689655171E-2</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.4827586206896551E-2</v>
       </c>
       <c r="H36" s="1">
@@ -1930,8 +2217,16 @@
         <f t="shared" si="3"/>
         <v>40.277777777777779</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <f t="shared" si="4"/>
+        <v>20880</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="5"/>
+        <v>69600</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1949,11 +2244,11 @@
         <v>0.10344827586206896</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>8.2758620689655171E-2</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.4827586206896551E-2</v>
       </c>
       <c r="H37" s="1">
@@ -1964,8 +2259,16 @@
         <f t="shared" si="3"/>
         <v>40.277777777777779</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <f t="shared" si="4"/>
+        <v>20880</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="5"/>
+        <v>69600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1983,11 +2286,11 @@
         <v>0.10344827586206896</v>
       </c>
       <c r="F38" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>8.2758620689655171E-2</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.4827586206896551E-2</v>
       </c>
       <c r="H38" s="1">
@@ -1998,8 +2301,16 @@
         <f t="shared" si="3"/>
         <v>40.277777777777779</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <f t="shared" si="4"/>
+        <v>20880</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="5"/>
+        <v>69600</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -2017,11 +2328,11 @@
         <v>0.17241379310344829</v>
       </c>
       <c r="F39" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.13793103448275865</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4.1379310344827593E-2</v>
       </c>
       <c r="H39" s="1">
@@ -2032,8 +2343,16 @@
         <f t="shared" si="3"/>
         <v>24.166666666666664</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <f t="shared" si="4"/>
+        <v>12527.999999999996</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="5"/>
+        <v>41759.999999999993</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -2051,11 +2370,11 @@
         <v>0.13793103448275862</v>
       </c>
       <c r="F40" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.1103448275862069</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>3.310344827586207E-2</v>
       </c>
       <c r="H40" s="1">
@@ -2066,8 +2385,16 @@
         <f t="shared" si="3"/>
         <v>30.208333333333332</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J40">
+        <f t="shared" si="4"/>
+        <v>15660</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="5"/>
+        <v>52200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>5</v>
       </c>
@@ -2085,11 +2412,11 @@
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="F41" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2.7586206896551724E-2</v>
       </c>
       <c r="G41" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8.2758620689655175E-3</v>
       </c>
       <c r="H41" s="3">
@@ -2100,8 +2427,16 @@
         <f t="shared" si="3"/>
         <v>120.83333333333333</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J41">
+        <f t="shared" si="4"/>
+        <v>62640</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="5"/>
+        <v>208800</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>4</v>
       </c>
@@ -2123,7 +2458,7 @@
         <v>0.22499999999999998</v>
       </c>
       <c r="G42" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.7499999999999991E-2</v>
       </c>
       <c r="H42" s="3">
@@ -2134,8 +2469,16 @@
         <f t="shared" si="3"/>
         <v>14.814814814814817</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42">
+        <f t="shared" si="4"/>
+        <v>7680</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="5"/>
+        <v>25600.000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -2153,11 +2496,11 @@
         <v>0.3</v>
       </c>
       <c r="F43" s="1">
-        <f t="shared" ref="F43:F46" si="8">0.75*E43*(C43+D43)/2</f>
+        <f t="shared" ref="F43:F46" si="10">0.75*E43*(C43+D43)/2</f>
         <v>0.22499999999999998</v>
       </c>
       <c r="G43" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.7499999999999991E-2</v>
       </c>
       <c r="H43" s="1">
@@ -2168,8 +2511,16 @@
         <f t="shared" si="3"/>
         <v>14.814814814814817</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <f t="shared" si="4"/>
+        <v>7680</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="5"/>
+        <v>25600.000000000004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2187,11 +2538,11 @@
         <v>0.2</v>
       </c>
       <c r="F44" s="1">
+        <f t="shared" si="10"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G44" s="1">
         <f t="shared" si="8"/>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="G44" s="1">
-        <f t="shared" si="6"/>
         <v>4.5000000000000005E-2</v>
       </c>
       <c r="H44" s="1">
@@ -2202,8 +2553,16 @@
         <f t="shared" si="3"/>
         <v>22.222222222222218</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44">
+        <f t="shared" si="4"/>
+        <v>11519.999999999998</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="5"/>
+        <v>38399.999999999993</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -2221,11 +2580,11 @@
         <v>0.1</v>
       </c>
       <c r="F45" s="1">
+        <f t="shared" si="10"/>
+        <v>7.5000000000000011E-2</v>
+      </c>
+      <c r="G45" s="1">
         <f t="shared" si="8"/>
-        <v>7.5000000000000011E-2</v>
-      </c>
-      <c r="G45" s="1">
-        <f t="shared" si="6"/>
         <v>2.2500000000000003E-2</v>
       </c>
       <c r="H45" s="1">
@@ -2236,8 +2595,16 @@
         <f t="shared" si="3"/>
         <v>44.444444444444436</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J45">
+        <f t="shared" si="4"/>
+        <v>23039.999999999996</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="5"/>
+        <v>76799.999999999985</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>4</v>
       </c>
@@ -2255,11 +2622,11 @@
         <v>0.1</v>
       </c>
       <c r="F46" s="3">
+        <f t="shared" si="10"/>
+        <v>7.5000000000000011E-2</v>
+      </c>
+      <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>7.5000000000000011E-2</v>
-      </c>
-      <c r="G46" s="3">
-        <f t="shared" si="6"/>
         <v>2.2500000000000003E-2</v>
       </c>
       <c r="H46" s="3">
@@ -2269,6 +2636,14 @@
       <c r="I46" s="3">
         <f t="shared" si="3"/>
         <v>44.444444444444436</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="4"/>
+        <v>23039.999999999996</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="5"/>
+        <v>76799.999999999985</v>
       </c>
     </row>
   </sheetData>

--- a/方块 block/试炼和宝库.xlsx
+++ b/方块 block/试炼和宝库.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\方块 block\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079FDD40-3E0F-4011-8452-33555790057F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2BCEB9-A44E-42C1-80DE-08608D4E6A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,7 +302,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +319,32 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -347,11 +373,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -816,27 +845,27 @@
         <v>0.16</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F31" si="0">2.2*E3*(C3+D3)/2</f>
+        <f>2.2*E3*(C3+D3)/2</f>
         <v>1.7600000000000002</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G26" si="1">F3*0.5</f>
+        <f>F3*0.5</f>
         <v>0.88000000000000012</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H46" si="2">1/F3</f>
+        <f>1/F3</f>
         <v>0.56818181818181812</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3:I46" si="3">1/G3</f>
+        <f>1/G3</f>
         <v>1.1363636363636362</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J46" si="4">H3*1728</f>
+        <f>H3*1728</f>
         <v>981.81818181818176</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K46" si="5">I3*1728</f>
+        <f>I3*1728</f>
         <v>1963.6363636363635</v>
       </c>
     </row>
@@ -858,27 +887,27 @@
         <v>0.12</v>
       </c>
       <c r="F4" s="3">
-        <f t="shared" si="0"/>
+        <f>2.2*E4*(C4+D4)/2</f>
         <v>0.52800000000000002</v>
       </c>
       <c r="G4" s="3">
-        <f t="shared" si="1"/>
+        <f>F4*0.5</f>
         <v>0.26400000000000001</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F4</f>
         <v>1.8939393939393938</v>
       </c>
       <c r="I4" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G4</f>
         <v>3.7878787878787876</v>
       </c>
       <c r="J4">
-        <f t="shared" si="4"/>
+        <f>H4*1728</f>
         <v>3272.7272727272725</v>
       </c>
       <c r="K4">
-        <f t="shared" si="5"/>
+        <f>I4*1728</f>
         <v>6545.454545454545</v>
       </c>
     </row>
@@ -900,27 +929,27 @@
         <v>0.04</v>
       </c>
       <c r="F5" s="3">
-        <f t="shared" si="0"/>
+        <f>2.2*E5*(C5+D5)/2</f>
         <v>0.70400000000000007</v>
       </c>
       <c r="G5" s="3">
-        <f t="shared" si="1"/>
+        <f>F5*0.5</f>
         <v>0.35200000000000004</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F5</f>
         <v>1.4204545454545454</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G5</f>
         <v>2.8409090909090908</v>
       </c>
       <c r="J5">
-        <f t="shared" si="4"/>
+        <f>H5*1728</f>
         <v>2454.5454545454545</v>
       </c>
       <c r="K5">
-        <f t="shared" si="5"/>
+        <f>I5*1728</f>
         <v>4909.090909090909</v>
       </c>
     </row>
@@ -942,27 +971,27 @@
         <v>0.12</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="0"/>
+        <f>2.2*E6*(C6+D6)/2</f>
         <v>0.66</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="1"/>
+        <f>F6*0.5</f>
         <v>0.33</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F6</f>
         <v>1.5151515151515151</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G6</f>
         <v>3.0303030303030303</v>
       </c>
       <c r="J6">
-        <f t="shared" si="4"/>
+        <f>H6*1728</f>
         <v>2618.181818181818</v>
       </c>
       <c r="K6">
-        <f t="shared" si="5"/>
+        <f>I6*1728</f>
         <v>5236.363636363636</v>
       </c>
     </row>
@@ -984,27 +1013,27 @@
         <v>0.16</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="0"/>
+        <f>2.2*E7*(C7+D7)/2</f>
         <v>1.056</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="1"/>
+        <f>F7*0.5</f>
         <v>0.52800000000000002</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F7</f>
         <v>0.94696969696969691</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G7</f>
         <v>1.8939393939393938</v>
       </c>
       <c r="J7">
-        <f t="shared" si="4"/>
+        <f>H7*1728</f>
         <v>1636.3636363636363</v>
       </c>
       <c r="K7">
-        <f t="shared" si="5"/>
+        <f>I7*1728</f>
         <v>3272.7272727272725</v>
       </c>
     </row>
@@ -1026,27 +1055,27 @@
         <v>0.04</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="0"/>
+        <f>2.2*E8*(C8+D8)/2</f>
         <v>0.13200000000000001</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="1"/>
+        <f>F8*0.5</f>
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F8</f>
         <v>7.5757575757575752</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G8</f>
         <v>15.15151515151515</v>
       </c>
       <c r="J8">
-        <f t="shared" si="4"/>
+        <f>H8*1728</f>
         <v>13090.90909090909</v>
       </c>
       <c r="K8">
-        <f t="shared" si="5"/>
+        <f>I8*1728</f>
         <v>26181.81818181818</v>
       </c>
     </row>
@@ -1068,27 +1097,27 @@
         <v>0.12</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="0"/>
+        <f>2.2*E9*(C9+D9)/2</f>
         <v>0.39600000000000002</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="1"/>
+        <f>F9*0.5</f>
         <v>0.19800000000000001</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F9</f>
         <v>2.5252525252525251</v>
       </c>
       <c r="I9" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G9</f>
         <v>5.0505050505050502</v>
       </c>
       <c r="J9">
-        <f t="shared" si="4"/>
+        <f>H9*1728</f>
         <v>4363.6363636363631</v>
       </c>
       <c r="K9">
-        <f t="shared" si="5"/>
+        <f>I9*1728</f>
         <v>8727.2727272727261</v>
       </c>
     </row>
@@ -1110,27 +1139,27 @@
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="0"/>
+        <f>2.2*E10*(C10+D10)/2</f>
         <v>0.17600000000000002</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="1"/>
+        <f>F10*0.5</f>
         <v>8.8000000000000009E-2</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F10</f>
         <v>5.6818181818181817</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G10</f>
         <v>11.363636363636363</v>
       </c>
       <c r="J10">
-        <f t="shared" si="4"/>
+        <f>H10*1728</f>
         <v>9818.181818181818</v>
       </c>
       <c r="K10">
-        <f t="shared" si="5"/>
+        <f>I10*1728</f>
         <v>19636.363636363636</v>
       </c>
     </row>
@@ -1156,23 +1185,23 @@
         <v>0.31304347826086959</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="1"/>
+        <f>F11*0.5</f>
         <v>0.15652173913043479</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F11</f>
         <v>3.1944444444444442</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G11</f>
         <v>6.3888888888888884</v>
       </c>
       <c r="J11">
-        <f t="shared" si="4"/>
+        <f>H11*1728</f>
         <v>5520</v>
       </c>
       <c r="K11">
-        <f t="shared" si="5"/>
+        <f>I11*1728</f>
         <v>11040</v>
       </c>
     </row>
@@ -1194,27 +1223,27 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" ref="F12:F21" si="6">0.8*E12*(C12+D12)/2</f>
+        <f>0.8*E12*(C12+D12)/2</f>
         <v>0.10434782608695653</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="1"/>
+        <f>F12*0.5</f>
         <v>5.2173913043478265E-2</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F12</f>
         <v>9.5833333333333321</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G12</f>
         <v>19.166666666666664</v>
       </c>
       <c r="J12">
-        <f t="shared" si="4"/>
+        <f>H12*1728</f>
         <v>16559.999999999996</v>
       </c>
       <c r="K12">
-        <f t="shared" si="5"/>
+        <f>I12*1728</f>
         <v>33119.999999999993</v>
       </c>
     </row>
@@ -1222,7 +1251,7 @@
       <c r="A13" t="s">
         <v>1</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="1">
@@ -1236,35 +1265,35 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E13*(C13+D13)/2</f>
         <v>0.10434782608695653</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="1"/>
+        <f>F13*0.5</f>
         <v>5.2173913043478265E-2</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F13</f>
         <v>9.5833333333333321</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G13</f>
         <v>19.166666666666664</v>
       </c>
-      <c r="J13">
-        <f t="shared" si="4"/>
+      <c r="J13" s="5">
+        <f>H13*1728</f>
         <v>16559.999999999996</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="5"/>
-        <v>33119.999999999993</v>
+      <c r="K13" s="5">
+        <f>I13*27</f>
+        <v>517.49999999999989</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1">
@@ -1278,35 +1307,35 @@
         <v>0.13043478260869565</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E14*(C14+D14)/2</f>
         <v>0.10434782608695653</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="1"/>
+        <f>F14*0.5</f>
         <v>5.2173913043478265E-2</v>
       </c>
       <c r="H14" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F14</f>
         <v>9.5833333333333321</v>
       </c>
       <c r="I14" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G14</f>
         <v>19.166666666666664</v>
       </c>
-      <c r="J14">
-        <f t="shared" si="4"/>
+      <c r="J14" s="5">
+        <f>H14*1728</f>
         <v>16559.999999999996</v>
       </c>
-      <c r="K14">
-        <f t="shared" si="5"/>
-        <v>33119.999999999993</v>
+      <c r="K14" s="5">
+        <f>I14*27</f>
+        <v>517.49999999999989</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="1">
@@ -1320,35 +1349,35 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E15*(C15+D15)/2</f>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="1"/>
+        <f>F15*0.5</f>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F15</f>
         <v>14.375</v>
       </c>
       <c r="I15" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G15</f>
         <v>28.75</v>
       </c>
-      <c r="J15">
-        <f t="shared" si="4"/>
+      <c r="J15" s="5">
+        <f>H15*1728</f>
         <v>24840</v>
       </c>
-      <c r="K15">
-        <f t="shared" si="5"/>
-        <v>49680</v>
+      <c r="K15" s="5">
+        <f>I15*27</f>
+        <v>776.25</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="1">
@@ -1362,35 +1391,35 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E16*(C16+D16)/2</f>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="1"/>
+        <f>F16*0.5</f>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F16</f>
         <v>14.375</v>
       </c>
       <c r="I16" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G16</f>
         <v>28.75</v>
       </c>
-      <c r="J16">
-        <f t="shared" si="4"/>
+      <c r="J16" s="5">
+        <f>H16*1728</f>
         <v>24840</v>
       </c>
-      <c r="K16">
-        <f t="shared" si="5"/>
-        <v>49680</v>
+      <c r="K16" s="5">
+        <f>I16*27</f>
+        <v>776.25</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="1">
@@ -1404,35 +1433,35 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E17*(C17+D17)/2</f>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="1"/>
+        <f>F17*0.5</f>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="H17" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F17</f>
         <v>14.375</v>
       </c>
       <c r="I17" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G17</f>
         <v>28.75</v>
       </c>
-      <c r="J17">
-        <f t="shared" si="4"/>
+      <c r="J17" s="5">
+        <f>H17*1728</f>
         <v>24840</v>
       </c>
-      <c r="K17">
-        <f t="shared" si="5"/>
-        <v>49680</v>
+      <c r="K17" s="5">
+        <f>I17*27</f>
+        <v>776.25</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="1">
@@ -1446,35 +1475,35 @@
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E18*(C18+D18)/2</f>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="1"/>
+        <f>F18*0.5</f>
         <v>1.7391304347826087E-2</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F18</f>
         <v>28.75</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G18</f>
         <v>57.5</v>
       </c>
-      <c r="J18">
-        <f t="shared" si="4"/>
+      <c r="J18" s="5">
+        <f>H18*1728</f>
         <v>49680</v>
       </c>
-      <c r="K18">
-        <f t="shared" si="5"/>
-        <v>99360</v>
+      <c r="K18" s="5">
+        <f>I18*27</f>
+        <v>1552.5</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="1">
@@ -1488,35 +1517,35 @@
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E19*(C19+D19)/2</f>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="1"/>
+        <f>F19*0.5</f>
         <v>1.7391304347826087E-2</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F19</f>
         <v>28.75</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G19</f>
         <v>57.5</v>
       </c>
-      <c r="J19">
-        <f t="shared" si="4"/>
+      <c r="J19" s="5">
+        <f>H19*1728</f>
         <v>49680</v>
       </c>
-      <c r="K19">
-        <f t="shared" si="5"/>
-        <v>99360</v>
+      <c r="K19" s="5">
+        <f>I19*27</f>
+        <v>1552.5</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="1">
@@ -1530,35 +1559,35 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E20*(C20+D20)/2</f>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="1"/>
+        <f>F20*0.5</f>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F20</f>
         <v>14.375</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G20</f>
         <v>28.75</v>
       </c>
-      <c r="J20">
-        <f t="shared" si="4"/>
+      <c r="J20" s="5">
+        <f>H20*1728</f>
         <v>24840</v>
       </c>
-      <c r="K20">
-        <f t="shared" si="5"/>
-        <v>49680</v>
+      <c r="K20" s="5">
+        <f>I20*27</f>
+        <v>776.25</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C21" s="1">
@@ -1572,28 +1601,28 @@
         <v>8.6956521739130432E-2</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="6"/>
+        <f>0.8*E21*(C21+D21)/2</f>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="1"/>
+        <f>F21*0.5</f>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F21</f>
         <v>14.375</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G21</f>
         <v>28.75</v>
       </c>
-      <c r="J21">
-        <f t="shared" si="4"/>
+      <c r="J21" s="5">
+        <f>H21*1728</f>
         <v>24840</v>
       </c>
-      <c r="K21">
-        <f t="shared" si="5"/>
-        <v>49680</v>
+      <c r="K21" s="5">
+        <f>I21*27</f>
+        <v>776.25</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1618,23 +1647,23 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="1"/>
+        <f>F22*0.5</f>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F22</f>
         <v>12</v>
       </c>
       <c r="I22" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G22</f>
         <v>24</v>
       </c>
       <c r="J22">
-        <f t="shared" si="4"/>
+        <f>H22*1728</f>
         <v>20736</v>
       </c>
       <c r="K22">
-        <f t="shared" si="5"/>
+        <f>I22*1728</f>
         <v>41472</v>
       </c>
     </row>
@@ -1656,27 +1685,27 @@
         <v>0.25</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" ref="F23:F26" si="7">0.25*E23*(C23+D23)/2</f>
+        <f>0.25*E23*(C23+D23)/2</f>
         <v>6.25E-2</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="1"/>
+        <f>F23*0.5</f>
         <v>3.125E-2</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F23</f>
         <v>16</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G23</f>
         <v>32</v>
       </c>
       <c r="J23">
-        <f t="shared" si="4"/>
+        <f>H23*1728</f>
         <v>27648</v>
       </c>
       <c r="K23">
-        <f t="shared" si="5"/>
+        <f>I23*1728</f>
         <v>55296</v>
       </c>
     </row>
@@ -1684,7 +1713,7 @@
       <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C24" s="1">
@@ -1698,35 +1727,35 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="7"/>
+        <f>0.25*E24*(C24+D24)/2</f>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="1"/>
+        <f>F24*0.5</f>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F24</f>
         <v>24</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G24</f>
         <v>48</v>
       </c>
-      <c r="J24">
-        <f t="shared" si="4"/>
+      <c r="J24" s="5">
+        <f>H24*1728</f>
         <v>41472</v>
       </c>
-      <c r="K24">
-        <f t="shared" si="5"/>
-        <v>82944</v>
+      <c r="K24" s="5">
+        <f>I24*27</f>
+        <v>1296</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="1">
@@ -1740,35 +1769,35 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="F25" s="1">
-        <f t="shared" si="7"/>
+        <f>0.25*E25*(C25+D25)/2</f>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="1"/>
+        <f>F25*0.5</f>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="H25" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F25</f>
         <v>24</v>
       </c>
       <c r="I25" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G25</f>
         <v>48</v>
       </c>
-      <c r="J25">
-        <f t="shared" si="4"/>
+      <c r="J25" s="5">
+        <f>H25*1728</f>
         <v>41472</v>
       </c>
-      <c r="K25">
-        <f t="shared" si="5"/>
-        <v>82944</v>
+      <c r="K25" s="5">
+        <f>I25*27</f>
+        <v>1296</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>2</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="1">
@@ -1782,28 +1811,28 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="7"/>
+        <f>0.25*E26*(C26+D26)/2</f>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="1"/>
+        <f>F26*0.5</f>
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="H26" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F26</f>
         <v>48</v>
       </c>
       <c r="I26" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G26</f>
         <v>96</v>
       </c>
       <c r="J26">
-        <f t="shared" si="4"/>
+        <f>H26*1728</f>
         <v>82944</v>
       </c>
       <c r="K26">
-        <f t="shared" si="5"/>
-        <v>165888</v>
+        <f>I26*27</f>
+        <v>2592</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -1824,7 +1853,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="F27" s="1">
-        <f t="shared" si="0"/>
+        <f>2.2*E27*(C27+D27)/2</f>
         <v>0.14666666666666667</v>
       </c>
       <c r="G27" s="1">
@@ -1832,19 +1861,19 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="H27" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F27</f>
         <v>6.8181818181818183</v>
       </c>
       <c r="I27" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G27</f>
         <v>22.72727272727273</v>
       </c>
       <c r="J27">
-        <f t="shared" si="4"/>
+        <f>H27*1728</f>
         <v>11781.818181818182</v>
       </c>
       <c r="K27">
-        <f t="shared" si="5"/>
+        <f>I27*1728</f>
         <v>39272.727272727279</v>
       </c>
     </row>
@@ -1866,27 +1895,27 @@
         <v>0.2</v>
       </c>
       <c r="F28" s="1">
-        <f t="shared" si="0"/>
+        <f>2.2*E28*(C28+D28)/2</f>
         <v>3.5200000000000005</v>
       </c>
       <c r="G28" s="1">
-        <f t="shared" ref="G28:G46" si="8">F28*0.3</f>
+        <f>F28*0.3</f>
         <v>1.056</v>
       </c>
       <c r="H28" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F28</f>
         <v>0.28409090909090906</v>
       </c>
       <c r="I28" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G28</f>
         <v>0.94696969696969691</v>
       </c>
       <c r="J28">
-        <f t="shared" si="4"/>
+        <f>H28*1728</f>
         <v>490.90909090909088</v>
       </c>
       <c r="K28">
-        <f t="shared" si="5"/>
+        <f>I28*1728</f>
         <v>1636.3636363636363</v>
       </c>
     </row>
@@ -1908,27 +1937,27 @@
         <v>0.26666666666666666</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="0"/>
+        <f>2.2*E29*(C29+D29)/2</f>
         <v>5.8666666666666671</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="8"/>
+        <f>F29*0.3</f>
         <v>1.76</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F29</f>
         <v>0.17045454545454544</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G29</f>
         <v>0.56818181818181823</v>
       </c>
       <c r="J29">
-        <f t="shared" si="4"/>
+        <f>H29*1728</f>
         <v>294.5454545454545</v>
       </c>
       <c r="K29">
-        <f t="shared" si="5"/>
+        <f>I29*1728</f>
         <v>981.81818181818187</v>
       </c>
     </row>
@@ -1950,27 +1979,27 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="F30" s="1">
-        <f t="shared" si="0"/>
+        <f>2.2*E30*(C30+D30)/2</f>
         <v>5.1333333333333337</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" si="8"/>
+        <f>F30*0.3</f>
         <v>1.54</v>
       </c>
       <c r="H30" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F30</f>
         <v>0.19480519480519479</v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G30</f>
         <v>0.64935064935064934</v>
       </c>
       <c r="J30">
-        <f t="shared" si="4"/>
+        <f>H30*1728</f>
         <v>336.6233766233766</v>
       </c>
       <c r="K30">
-        <f t="shared" si="5"/>
+        <f>I30*1728</f>
         <v>1122.077922077922</v>
       </c>
     </row>
@@ -1992,27 +2021,27 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="0"/>
+        <f>2.2*E31*(C31+D31)/2</f>
         <v>0.73333333333333339</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="8"/>
+        <f>F31*0.3</f>
         <v>0.22</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F31</f>
         <v>1.3636363636363635</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G31</f>
         <v>4.5454545454545459</v>
       </c>
       <c r="J31">
-        <f t="shared" si="4"/>
+        <f>H31*1728</f>
         <v>2356.363636363636</v>
       </c>
       <c r="K31">
-        <f t="shared" si="5"/>
+        <f>I31*1728</f>
         <v>7854.545454545455</v>
       </c>
     </row>
@@ -2020,7 +2049,7 @@
       <c r="A32" t="s">
         <v>5</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C32" s="1">
@@ -2038,31 +2067,31 @@
         <v>0.1103448275862069</v>
       </c>
       <c r="G32" s="1">
-        <f t="shared" si="8"/>
+        <f>F32*0.3</f>
         <v>3.310344827586207E-2</v>
       </c>
       <c r="H32" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F32</f>
         <v>9.0625</v>
       </c>
       <c r="I32" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G32</f>
         <v>30.208333333333332</v>
       </c>
-      <c r="J32">
-        <f t="shared" si="4"/>
+      <c r="J32" s="5">
+        <f>H32*1728</f>
         <v>15660</v>
       </c>
-      <c r="K32">
-        <f t="shared" si="5"/>
-        <v>52200</v>
+      <c r="K32" s="5">
+        <f>I32*27</f>
+        <v>815.625</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="1">
@@ -2076,35 +2105,35 @@
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="F33" s="1">
-        <f t="shared" ref="F33:F41" si="9">0.8*E33*(C33+D33)/2</f>
+        <f>0.8*E33*(C33+D33)/2</f>
         <v>5.5172413793103448E-2</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="8"/>
+        <f>F33*0.3</f>
         <v>1.6551724137931035E-2</v>
       </c>
       <c r="H33" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F33</f>
         <v>18.125</v>
       </c>
       <c r="I33" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G33</f>
         <v>60.416666666666664</v>
       </c>
-      <c r="J33">
-        <f t="shared" si="4"/>
+      <c r="J33" s="5">
+        <f>H33*1728</f>
         <v>31320</v>
       </c>
-      <c r="K33">
-        <f t="shared" si="5"/>
-        <v>104400</v>
+      <c r="K33" s="5">
+        <f>I33*27</f>
+        <v>1631.25</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="1">
@@ -2118,35 +2147,35 @@
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="9"/>
+        <f>0.8*E34*(C34+D34)/2</f>
         <v>5.5172413793103448E-2</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="8"/>
+        <f>F34*0.3</f>
         <v>1.6551724137931035E-2</v>
       </c>
       <c r="H34" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F34</f>
         <v>18.125</v>
       </c>
       <c r="I34" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G34</f>
         <v>60.416666666666664</v>
       </c>
-      <c r="J34">
-        <f t="shared" si="4"/>
+      <c r="J34" s="5">
+        <f>H34*1728</f>
         <v>31320</v>
       </c>
-      <c r="K34">
-        <f t="shared" si="5"/>
-        <v>104400</v>
+      <c r="K34" s="5">
+        <f>I34*27</f>
+        <v>1631.25</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C35" s="1">
@@ -2160,35 +2189,35 @@
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="F35" s="1">
-        <f t="shared" si="9"/>
+        <f>0.8*E35*(C35+D35)/2</f>
         <v>5.5172413793103448E-2</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" si="8"/>
+        <f>F35*0.3</f>
         <v>1.6551724137931035E-2</v>
       </c>
       <c r="H35" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F35</f>
         <v>18.125</v>
       </c>
       <c r="I35" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G35</f>
         <v>60.416666666666664</v>
       </c>
-      <c r="J35">
-        <f t="shared" si="4"/>
+      <c r="J35" s="5">
+        <f>H35*1728</f>
         <v>31320</v>
       </c>
-      <c r="K35">
-        <f t="shared" si="5"/>
-        <v>104400</v>
+      <c r="K35" s="5">
+        <f>I35*27</f>
+        <v>1631.25</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C36" s="1">
@@ -2202,35 +2231,35 @@
         <v>0.10344827586206896</v>
       </c>
       <c r="F36" s="1">
-        <f t="shared" si="9"/>
+        <f>0.8*E36*(C36+D36)/2</f>
         <v>8.2758620689655171E-2</v>
       </c>
       <c r="G36" s="1">
-        <f t="shared" si="8"/>
+        <f>F36*0.3</f>
         <v>2.4827586206896551E-2</v>
       </c>
       <c r="H36" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F36</f>
         <v>12.083333333333334</v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G36</f>
         <v>40.277777777777779</v>
       </c>
-      <c r="J36">
-        <f t="shared" si="4"/>
+      <c r="J36" s="5">
+        <f>H36*1728</f>
         <v>20880</v>
       </c>
-      <c r="K36">
-        <f t="shared" si="5"/>
-        <v>69600</v>
+      <c r="K36" s="5">
+        <f>I36*27</f>
+        <v>1087.5</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="1">
@@ -2244,28 +2273,28 @@
         <v>0.10344827586206896</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" si="9"/>
+        <f>0.8*E37*(C37+D37)/2</f>
         <v>8.2758620689655171E-2</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="8"/>
+        <f>F37*0.3</f>
         <v>2.4827586206896551E-2</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F37</f>
         <v>12.083333333333334</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G37</f>
         <v>40.277777777777779</v>
       </c>
-      <c r="J37">
-        <f t="shared" si="4"/>
+      <c r="J37" s="5">
+        <f>H37*1728</f>
         <v>20880</v>
       </c>
-      <c r="K37">
-        <f t="shared" si="5"/>
-        <v>69600</v>
+      <c r="K37" s="5">
+        <f>I37*27</f>
+        <v>1087.5</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -2286,27 +2315,27 @@
         <v>0.10344827586206896</v>
       </c>
       <c r="F38" s="1">
-        <f t="shared" si="9"/>
+        <f>0.8*E38*(C38+D38)/2</f>
         <v>8.2758620689655171E-2</v>
       </c>
       <c r="G38" s="1">
-        <f t="shared" si="8"/>
+        <f>F38*0.3</f>
         <v>2.4827586206896551E-2</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F38</f>
         <v>12.083333333333334</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G38</f>
         <v>40.277777777777779</v>
       </c>
       <c r="J38">
-        <f t="shared" si="4"/>
+        <f>H38*1728</f>
         <v>20880</v>
       </c>
       <c r="K38">
-        <f t="shared" si="5"/>
+        <f>I38*1728</f>
         <v>69600</v>
       </c>
     </row>
@@ -2328,27 +2357,27 @@
         <v>0.17241379310344829</v>
       </c>
       <c r="F39" s="1">
-        <f t="shared" si="9"/>
+        <f>0.8*E39*(C39+D39)/2</f>
         <v>0.13793103448275865</v>
       </c>
       <c r="G39" s="1">
-        <f t="shared" si="8"/>
+        <f>F39*0.3</f>
         <v>4.1379310344827593E-2</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F39</f>
         <v>7.2499999999999982</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G39</f>
         <v>24.166666666666664</v>
       </c>
       <c r="J39">
-        <f t="shared" si="4"/>
+        <f>H39*1728</f>
         <v>12527.999999999996</v>
       </c>
       <c r="K39">
-        <f t="shared" si="5"/>
+        <f>I39*1728</f>
         <v>41759.999999999993</v>
       </c>
     </row>
@@ -2370,27 +2399,27 @@
         <v>0.13793103448275862</v>
       </c>
       <c r="F40" s="1">
-        <f t="shared" si="9"/>
+        <f>0.8*E40*(C40+D40)/2</f>
         <v>0.1103448275862069</v>
       </c>
       <c r="G40" s="1">
-        <f t="shared" si="8"/>
+        <f>F40*0.3</f>
         <v>3.310344827586207E-2</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F40</f>
         <v>9.0625</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G40</f>
         <v>30.208333333333332</v>
       </c>
       <c r="J40">
-        <f t="shared" si="4"/>
+        <f>H40*1728</f>
         <v>15660</v>
       </c>
       <c r="K40">
-        <f t="shared" si="5"/>
+        <f>I40*1728</f>
         <v>52200</v>
       </c>
     </row>
@@ -2412,27 +2441,27 @@
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="F41" s="3">
-        <f t="shared" si="9"/>
+        <f>0.8*E41*(C41+D41)/2</f>
         <v>2.7586206896551724E-2</v>
       </c>
       <c r="G41" s="3">
-        <f t="shared" si="8"/>
+        <f>F41*0.3</f>
         <v>8.2758620689655175E-3</v>
       </c>
       <c r="H41" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F41</f>
         <v>36.25</v>
       </c>
       <c r="I41" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G41</f>
         <v>120.83333333333333</v>
       </c>
       <c r="J41">
-        <f t="shared" si="4"/>
+        <f>H41*1728</f>
         <v>62640</v>
       </c>
       <c r="K41">
-        <f t="shared" si="5"/>
+        <f>I41*1728</f>
         <v>208800</v>
       </c>
     </row>
@@ -2458,23 +2487,23 @@
         <v>0.22499999999999998</v>
       </c>
       <c r="G42" s="3">
-        <f t="shared" si="8"/>
+        <f>F42*0.3</f>
         <v>6.7499999999999991E-2</v>
       </c>
       <c r="H42" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F42</f>
         <v>4.4444444444444446</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G42</f>
         <v>14.814814814814817</v>
       </c>
       <c r="J42">
-        <f t="shared" si="4"/>
+        <f>H42*1728</f>
         <v>7680</v>
       </c>
       <c r="K42">
-        <f t="shared" si="5"/>
+        <f>I42*1728</f>
         <v>25600.000000000004</v>
       </c>
     </row>
@@ -2496,27 +2525,27 @@
         <v>0.3</v>
       </c>
       <c r="F43" s="1">
-        <f t="shared" ref="F43:F46" si="10">0.75*E43*(C43+D43)/2</f>
+        <f>0.75*E43*(C43+D43)/2</f>
         <v>0.22499999999999998</v>
       </c>
       <c r="G43" s="1">
-        <f t="shared" si="8"/>
+        <f>F43*0.3</f>
         <v>6.7499999999999991E-2</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F43</f>
         <v>4.4444444444444446</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G43</f>
         <v>14.814814814814817</v>
       </c>
       <c r="J43">
-        <f t="shared" si="4"/>
+        <f>H43*1728</f>
         <v>7680</v>
       </c>
       <c r="K43">
-        <f t="shared" si="5"/>
+        <f>I43*1728</f>
         <v>25600.000000000004</v>
       </c>
     </row>
@@ -2524,7 +2553,7 @@
       <c r="A44" t="s">
         <v>4</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C44" s="1">
@@ -2538,35 +2567,35 @@
         <v>0.2</v>
       </c>
       <c r="F44" s="1">
-        <f t="shared" si="10"/>
+        <f>0.75*E44*(C44+D44)/2</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="G44" s="1">
-        <f t="shared" si="8"/>
+        <f>F44*0.3</f>
         <v>4.5000000000000005E-2</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F44</f>
         <v>6.6666666666666661</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G44</f>
         <v>22.222222222222218</v>
       </c>
-      <c r="J44">
-        <f t="shared" si="4"/>
+      <c r="J44" s="5">
+        <f>H44*1728</f>
         <v>11519.999999999998</v>
       </c>
-      <c r="K44">
-        <f t="shared" si="5"/>
-        <v>38399.999999999993</v>
+      <c r="K44" s="5">
+        <f>I44*27</f>
+        <v>599.99999999999989</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>4</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C45" s="1">
@@ -2580,28 +2609,28 @@
         <v>0.1</v>
       </c>
       <c r="F45" s="1">
-        <f t="shared" si="10"/>
+        <f>0.75*E45*(C45+D45)/2</f>
         <v>7.5000000000000011E-2</v>
       </c>
       <c r="G45" s="1">
-        <f t="shared" si="8"/>
+        <f>F45*0.3</f>
         <v>2.2500000000000003E-2</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="2"/>
+        <f>1/F45</f>
         <v>13.333333333333332</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="3"/>
+        <f>1/G45</f>
         <v>44.444444444444436</v>
       </c>
-      <c r="J45">
-        <f t="shared" si="4"/>
+      <c r="J45" s="5">
+        <f>H45*1728</f>
         <v>23039.999999999996</v>
       </c>
-      <c r="K45">
-        <f t="shared" si="5"/>
-        <v>76799.999999999985</v>
+      <c r="K45" s="5">
+        <f>I45*27</f>
+        <v>1199.9999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2622,27 +2651,27 @@
         <v>0.1</v>
       </c>
       <c r="F46" s="3">
-        <f t="shared" si="10"/>
+        <f>0.75*E46*(C46+D46)/2</f>
         <v>7.5000000000000011E-2</v>
       </c>
       <c r="G46" s="3">
-        <f t="shared" si="8"/>
+        <f>F46*0.3</f>
         <v>2.2500000000000003E-2</v>
       </c>
       <c r="H46" s="3">
-        <f t="shared" si="2"/>
+        <f>1/F46</f>
         <v>13.333333333333332</v>
       </c>
       <c r="I46" s="3">
-        <f t="shared" si="3"/>
+        <f>1/G46</f>
         <v>44.444444444444436</v>
       </c>
       <c r="J46">
-        <f t="shared" si="4"/>
+        <f>H46*1728</f>
         <v>23039.999999999996</v>
       </c>
       <c r="K46">
-        <f t="shared" si="5"/>
+        <f>I46*1728</f>
         <v>76799.999999999985</v>
       </c>
     </row>

--- a/方块 block/试炼和宝库.xlsx
+++ b/方块 block/试炼和宝库.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\方块 block\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2BCEB9-A44E-42C1-80DE-08608D4E6A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA6C658-E382-40A9-A585-9D7C8F1E740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>普通</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,38 +95,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>弓(5~15附魔+宝藏)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>金胡萝卜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>钻石胸甲(5~15附魔+宝藏)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钻石斧(5~15附魔+宝藏)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁斧(0~10附魔+宝藏)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>弩(5~20附魔+宝藏)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>附魔书(三叉戟+精修)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁胸甲(0~10附魔+宝藏)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>钻石</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -143,14 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>钻石斧(10~20附魔+宝藏)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钻石胸甲(10~20附魔+宝藏)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>绿宝石块</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,22 +191,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>附魔书(杀手、工具、摔落缓冲)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>每个钥匙产量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>钥匙期望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>试炼次数期望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>单次试炼产量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -287,11 +243,67 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每盒的钥匙期望数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每盒的试炼期望次数</t>
+    <t>附魔书(两个杀手、工具、摔落缓冲)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附魔书(三叉戟、精修)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石斧(5~15附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石胸甲(5~15附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁斧(0~10附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁胸甲(0~10附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弩(5~20附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓(5~15附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石斧(10~20附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石胸甲(10~20附魔、宝藏)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每盒钥匙产量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个期望钥匙数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每盒的期望钥匙数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每盒的期望试炼次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个期望试炼次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -299,9 +311,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -375,12 +384,12 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -669,37 +678,37 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>2.2000000000000002</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>0.8</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>0.25</v>
@@ -707,7 +716,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>2.2000000000000002</v>
@@ -715,7 +724,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>0.8</v>
@@ -723,7 +732,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>0.75</v>
@@ -737,1941 +746,2307 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="4" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.08203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.08203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.4140625" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="18.25" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="C1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M1" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="5">
         <v>2</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="5">
         <v>8</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="5">
+        <f>AVERAGE(C2:D2)</f>
+        <v>5</v>
+      </c>
+      <c r="F2" s="5">
         <f>4/25</f>
         <v>0.16</v>
       </c>
-      <c r="F2" s="1">
-        <f>2.2*E2*(C2+D2)/2</f>
+      <c r="G2" s="5">
+        <f>2.2*F2*E2</f>
         <v>1.7600000000000002</v>
       </c>
-      <c r="G2" s="1">
-        <f>F2*0.5</f>
+      <c r="H2" s="5">
+        <f>G2*1728</f>
+        <v>3041.28</v>
+      </c>
+      <c r="I2" s="5">
+        <f t="shared" ref="I2:I26" si="0">G2*0.5</f>
         <v>0.88000000000000012</v>
       </c>
-      <c r="H2" s="1">
-        <f>1/F2</f>
+      <c r="J2" s="5">
+        <f t="shared" ref="J2:J46" si="1">1/G2</f>
         <v>0.56818181818181812</v>
       </c>
-      <c r="I2" s="1">
-        <f>1/G2</f>
+      <c r="K2" s="5">
+        <f t="shared" ref="K2:K46" si="2">1/I2</f>
         <v>1.1363636363636362</v>
       </c>
-      <c r="J2">
-        <f>H2*1728</f>
+      <c r="L2" s="5">
+        <f t="shared" ref="L2:L12" si="3">J2*1728</f>
         <v>981.81818181818176</v>
       </c>
-      <c r="K2">
-        <f>I2*1728</f>
+      <c r="M2" s="5">
+        <f t="shared" ref="M2:M12" si="4">K2*1728</f>
         <v>1963.6363636363635</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="5">
         <v>2</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="5">
         <v>8</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E46" si="5">AVERAGE(C3:D3)</f>
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
         <f>4/25</f>
         <v>0.16</v>
       </c>
-      <c r="F3" s="1">
-        <f>2.2*E3*(C3+D3)/2</f>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G10" si="6">2.2*F3*E3</f>
         <v>1.7600000000000002</v>
       </c>
-      <c r="G3" s="1">
-        <f>F3*0.5</f>
+      <c r="H3" s="5">
+        <f t="shared" ref="H3:H46" si="7">G3*1728</f>
+        <v>3041.28</v>
+      </c>
+      <c r="I3" s="5">
+        <f t="shared" si="0"/>
         <v>0.88000000000000012</v>
       </c>
-      <c r="H3" s="1">
-        <f>1/F3</f>
+      <c r="J3" s="5">
+        <f t="shared" si="1"/>
         <v>0.56818181818181812</v>
       </c>
-      <c r="I3" s="1">
-        <f>1/G3</f>
+      <c r="K3" s="5">
+        <f t="shared" si="2"/>
         <v>1.1363636363636362</v>
       </c>
-      <c r="J3">
-        <f>H3*1728</f>
+      <c r="L3" s="5">
+        <f t="shared" si="3"/>
         <v>981.81818181818176</v>
       </c>
-      <c r="K3">
-        <f>I3*1728</f>
+      <c r="M3" s="5">
+        <f t="shared" si="4"/>
         <v>1963.6363636363635</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
         <f>3/25</f>
         <v>0.12</v>
       </c>
-      <c r="F4" s="3">
-        <f>2.2*E4*(C4+D4)/2</f>
+      <c r="G4" s="5">
+        <f t="shared" si="6"/>
         <v>0.52800000000000002</v>
       </c>
-      <c r="G4" s="3">
-        <f>F4*0.5</f>
+      <c r="H4" s="5">
+        <f t="shared" si="7"/>
+        <v>912.38400000000001</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
         <v>0.26400000000000001</v>
       </c>
-      <c r="H4" s="3">
-        <f>1/F4</f>
+      <c r="J4" s="4">
+        <f t="shared" si="1"/>
         <v>1.8939393939393938</v>
       </c>
-      <c r="I4" s="3">
-        <f>1/G4</f>
+      <c r="K4" s="4">
+        <f t="shared" si="2"/>
         <v>3.7878787878787876</v>
       </c>
-      <c r="J4">
-        <f>H4*1728</f>
+      <c r="L4" s="5">
+        <f t="shared" si="3"/>
         <v>3272.7272727272725</v>
       </c>
-      <c r="K4">
-        <f>I4*1728</f>
+      <c r="M4" s="5">
+        <f t="shared" si="4"/>
         <v>6545.454545454545</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>12</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="F5" s="4">
         <f>1/25</f>
         <v>0.04</v>
       </c>
-      <c r="F5" s="3">
-        <f>2.2*E5*(C5+D5)/2</f>
+      <c r="G5" s="5">
+        <f t="shared" si="6"/>
         <v>0.70400000000000007</v>
       </c>
-      <c r="G5" s="3">
-        <f>F5*0.5</f>
+      <c r="H5" s="5">
+        <f t="shared" si="7"/>
+        <v>1216.5120000000002</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
         <v>0.35200000000000004</v>
       </c>
-      <c r="H5" s="3">
-        <f>1/F5</f>
+      <c r="J5" s="4">
+        <f t="shared" si="1"/>
         <v>1.4204545454545454</v>
       </c>
-      <c r="I5" s="3">
-        <f>1/G5</f>
+      <c r="K5" s="4">
+        <f t="shared" si="2"/>
         <v>2.8409090909090908</v>
       </c>
-      <c r="J5">
-        <f>H5*1728</f>
+      <c r="L5" s="5">
+        <f t="shared" si="3"/>
         <v>2454.5454545454545</v>
       </c>
-      <c r="K5">
-        <f>I5*1728</f>
+      <c r="M5" s="5">
+        <f t="shared" si="4"/>
         <v>4909.090909090909</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
         <v>4</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="5">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+      <c r="F6" s="5">
         <f>3/25</f>
         <v>0.12</v>
       </c>
-      <c r="F6" s="1">
-        <f>2.2*E6*(C6+D6)/2</f>
+      <c r="G6" s="5">
+        <f t="shared" si="6"/>
         <v>0.66</v>
       </c>
-      <c r="G6" s="1">
-        <f>F6*0.5</f>
+      <c r="H6" s="5">
+        <f t="shared" si="7"/>
+        <v>1140.48</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
         <v>0.33</v>
       </c>
-      <c r="H6" s="1">
-        <f>1/F6</f>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
         <v>1.5151515151515151</v>
       </c>
-      <c r="I6" s="1">
-        <f>1/G6</f>
+      <c r="K6" s="5">
+        <f t="shared" si="2"/>
         <v>3.0303030303030303</v>
       </c>
-      <c r="J6">
-        <f>H6*1728</f>
+      <c r="L6" s="5">
+        <f t="shared" si="3"/>
         <v>2618.181818181818</v>
       </c>
-      <c r="K6">
-        <f>I6*1728</f>
+      <c r="M6" s="5">
+        <f t="shared" si="4"/>
         <v>5236.363636363636</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>2</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="5">
         <v>4</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="5">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F7" s="5">
         <f>4/25</f>
         <v>0.16</v>
       </c>
-      <c r="F7" s="1">
-        <f>2.2*E7*(C7+D7)/2</f>
+      <c r="G7" s="5">
+        <f t="shared" si="6"/>
         <v>1.056</v>
       </c>
-      <c r="G7" s="1">
-        <f>F7*0.5</f>
+      <c r="H7" s="5">
+        <f t="shared" si="7"/>
+        <v>1824.768</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
         <v>0.52800000000000002</v>
       </c>
-      <c r="H7" s="1">
-        <f>1/F7</f>
+      <c r="J7" s="5">
+        <f t="shared" si="1"/>
         <v>0.94696969696969691</v>
       </c>
-      <c r="I7" s="1">
-        <f>1/G7</f>
+      <c r="K7" s="5">
+        <f t="shared" si="2"/>
         <v>1.8939393939393938</v>
       </c>
-      <c r="J7">
-        <f>H7*1728</f>
+      <c r="L7" s="5">
+        <f t="shared" si="3"/>
         <v>1636.3636363636363</v>
       </c>
-      <c r="K7">
-        <f>I7*1728</f>
+      <c r="M7" s="5">
+        <f t="shared" si="4"/>
         <v>3272.7272727272725</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="4">
         <f>1/25</f>
         <v>0.04</v>
       </c>
-      <c r="F8" s="3">
-        <f>2.2*E8*(C8+D8)/2</f>
+      <c r="G8" s="5">
+        <f t="shared" si="6"/>
         <v>0.13200000000000001</v>
       </c>
-      <c r="G8" s="3">
-        <f>F8*0.5</f>
+      <c r="H8" s="5">
+        <f t="shared" si="7"/>
+        <v>228.096</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="H8" s="3">
-        <f>1/F8</f>
+      <c r="J8" s="4">
+        <f t="shared" si="1"/>
         <v>7.5757575757575752</v>
       </c>
-      <c r="I8" s="3">
-        <f>1/G8</f>
+      <c r="K8" s="4">
+        <f t="shared" si="2"/>
         <v>15.15151515151515</v>
       </c>
-      <c r="J8">
-        <f>H8*1728</f>
+      <c r="L8" s="5">
+        <f t="shared" si="3"/>
         <v>13090.90909090909</v>
       </c>
-      <c r="K8">
-        <f>I8*1728</f>
+      <c r="M8" s="5">
+        <f t="shared" si="4"/>
         <v>26181.81818181818</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
         <v>2</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="5">
         <f>3/25</f>
         <v>0.12</v>
       </c>
-      <c r="F9" s="1">
-        <f>2.2*E9*(C9+D9)/2</f>
+      <c r="G9" s="5">
+        <f t="shared" si="6"/>
         <v>0.39600000000000002</v>
       </c>
-      <c r="G9" s="1">
-        <f>F9*0.5</f>
+      <c r="H9" s="5">
+        <f t="shared" si="7"/>
+        <v>684.28800000000001</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="0"/>
         <v>0.19800000000000001</v>
       </c>
-      <c r="H9" s="1">
-        <f>1/F9</f>
+      <c r="J9" s="5">
+        <f t="shared" si="1"/>
         <v>2.5252525252525251</v>
       </c>
-      <c r="I9" s="1">
-        <f>1/G9</f>
+      <c r="K9" s="5">
+        <f t="shared" si="2"/>
         <v>5.0505050505050502</v>
       </c>
-      <c r="J9">
-        <f>H9*1728</f>
+      <c r="L9" s="5">
+        <f t="shared" si="3"/>
         <v>4363.6363636363631</v>
       </c>
-      <c r="K9">
-        <f>I9*1728</f>
+      <c r="M9" s="5">
+        <f t="shared" si="4"/>
         <v>8727.2727272727261</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
+        <v>34</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
         <f>2/25</f>
         <v>0.08</v>
       </c>
-      <c r="F10" s="1">
-        <f>2.2*E10*(C10+D10)/2</f>
+      <c r="G10" s="5">
+        <f t="shared" si="6"/>
         <v>0.17600000000000002</v>
       </c>
-      <c r="G10" s="1">
-        <f>F10*0.5</f>
+      <c r="H10" s="5">
+        <f t="shared" si="7"/>
+        <v>304.12800000000004</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
         <v>8.8000000000000009E-2</v>
       </c>
-      <c r="H10" s="1">
-        <f>1/F10</f>
+      <c r="J10" s="5">
+        <f t="shared" si="1"/>
         <v>5.6818181818181817</v>
       </c>
-      <c r="I10" s="1">
-        <f>1/G10</f>
+      <c r="K10" s="5">
+        <f t="shared" si="2"/>
         <v>11.363636363636363</v>
       </c>
-      <c r="J10">
-        <f>H10*1728</f>
+      <c r="L10" s="5">
+        <f t="shared" si="3"/>
         <v>9818.181818181818</v>
       </c>
-      <c r="K10">
-        <f>I10*1728</f>
+      <c r="M10" s="5">
+        <f t="shared" si="4"/>
         <v>19636.363636363636</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="5">
         <v>2</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="5">
         <v>4</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="5">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="F11" s="5">
         <f>3/23</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="F11" s="1">
-        <f>0.8*E11*(C11+D11)/2</f>
+      <c r="G11" s="5">
+        <f>0.8*F11*E11</f>
         <v>0.31304347826086959</v>
       </c>
-      <c r="G11" s="1">
-        <f>F11*0.5</f>
+      <c r="H11" s="5">
+        <f t="shared" si="7"/>
+        <v>540.93913043478267</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
         <v>0.15652173913043479</v>
       </c>
-      <c r="H11" s="1">
-        <f>1/F11</f>
+      <c r="J11" s="5">
+        <f t="shared" si="1"/>
         <v>3.1944444444444442</v>
       </c>
-      <c r="I11" s="1">
-        <f>1/G11</f>
+      <c r="K11" s="5">
+        <f t="shared" si="2"/>
         <v>6.3888888888888884</v>
       </c>
-      <c r="J11">
-        <f>H11*1728</f>
+      <c r="L11" s="5">
+        <f t="shared" si="3"/>
         <v>5520</v>
       </c>
-      <c r="K11">
-        <f>I11*1728</f>
+      <c r="M11" s="5">
+        <f t="shared" si="4"/>
         <v>11040</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
         <v>2</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+      <c r="F12" s="5">
         <f>2/23</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="F12" s="1">
-        <f>0.8*E12*(C12+D12)/2</f>
+      <c r="G12" s="5">
+        <f t="shared" ref="G12:G21" si="8">0.8*F12*E12</f>
         <v>0.10434782608695653</v>
       </c>
-      <c r="G12" s="1">
-        <f>F12*0.5</f>
+      <c r="H12" s="5">
+        <f t="shared" si="7"/>
+        <v>180.31304347826088</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
         <v>5.2173913043478265E-2</v>
       </c>
-      <c r="H12" s="1">
-        <f>1/F12</f>
+      <c r="J12" s="5">
+        <f t="shared" si="1"/>
         <v>9.5833333333333321</v>
       </c>
-      <c r="I12" s="1">
-        <f>1/G12</f>
+      <c r="K12" s="5">
+        <f t="shared" si="2"/>
         <v>19.166666666666664</v>
       </c>
-      <c r="J12">
-        <f>H12*1728</f>
+      <c r="L12" s="5">
+        <f t="shared" si="3"/>
         <v>16559.999999999996</v>
       </c>
-      <c r="K12">
-        <f>I12*1728</f>
+      <c r="M12" s="5">
+        <f t="shared" si="4"/>
         <v>33119.999999999993</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
         <f>3/23</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="F13" s="1">
-        <f>0.8*E13*(C13+D13)/2</f>
+      <c r="G13" s="5">
+        <f t="shared" si="8"/>
         <v>0.10434782608695653</v>
       </c>
-      <c r="G13" s="1">
-        <f>F13*0.5</f>
+      <c r="H13" s="5">
+        <f t="shared" si="7"/>
+        <v>180.31304347826088</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="0"/>
         <v>5.2173913043478265E-2</v>
       </c>
-      <c r="H13" s="1">
-        <f>1/F13</f>
+      <c r="J13" s="5">
+        <f t="shared" si="1"/>
         <v>9.5833333333333321</v>
       </c>
-      <c r="I13" s="1">
-        <f>1/G13</f>
+      <c r="K13" s="5">
+        <f t="shared" si="2"/>
         <v>19.166666666666664</v>
       </c>
-      <c r="J13" s="5">
-        <f>H13*1728</f>
+      <c r="L13" s="6">
+        <f t="shared" ref="L13:L46" si="9">J13*1728</f>
         <v>16559.999999999996</v>
       </c>
-      <c r="K13" s="5">
-        <f>I13*27</f>
+      <c r="M13" s="6">
+        <f t="shared" ref="M13:M21" si="10">K13*27</f>
         <v>517.49999999999989</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="B14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F14" s="5">
         <f>3/23</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="F14" s="1">
-        <f>0.8*E14*(C14+D14)/2</f>
+      <c r="G14" s="5">
+        <f t="shared" si="8"/>
         <v>0.10434782608695653</v>
       </c>
-      <c r="G14" s="1">
-        <f>F14*0.5</f>
+      <c r="H14" s="5">
+        <f t="shared" si="7"/>
+        <v>180.31304347826088</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
         <v>5.2173913043478265E-2</v>
       </c>
-      <c r="H14" s="1">
-        <f>1/F14</f>
+      <c r="J14" s="5">
+        <f t="shared" si="1"/>
         <v>9.5833333333333321</v>
       </c>
-      <c r="I14" s="1">
-        <f>1/G14</f>
+      <c r="K14" s="5">
+        <f t="shared" si="2"/>
         <v>19.166666666666664</v>
       </c>
-      <c r="J14" s="5">
-        <f>H14*1728</f>
+      <c r="L14" s="6">
+        <f t="shared" si="9"/>
         <v>16559.999999999996</v>
       </c>
-      <c r="K14" s="5">
-        <f>I14*27</f>
+      <c r="M14" s="6">
+        <f t="shared" si="10"/>
         <v>517.49999999999989</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
         <f>2/23</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="F15" s="1">
-        <f>0.8*E15*(C15+D15)/2</f>
+      <c r="G15" s="5">
+        <f t="shared" si="8"/>
         <v>6.9565217391304349E-2</v>
       </c>
-      <c r="G15" s="1">
-        <f>F15*0.5</f>
+      <c r="H15" s="5">
+        <f t="shared" si="7"/>
+        <v>120.20869565217392</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
         <v>3.4782608695652174E-2</v>
       </c>
-      <c r="H15" s="1">
-        <f>1/F15</f>
+      <c r="J15" s="5">
+        <f t="shared" si="1"/>
         <v>14.375</v>
       </c>
-      <c r="I15" s="1">
-        <f>1/G15</f>
+      <c r="K15" s="5">
+        <f t="shared" si="2"/>
         <v>28.75</v>
       </c>
-      <c r="J15" s="5">
-        <f>H15*1728</f>
+      <c r="L15" s="6">
+        <f t="shared" si="9"/>
         <v>24840</v>
       </c>
-      <c r="K15" s="5">
-        <f>I15*27</f>
+      <c r="M15" s="6">
+        <f t="shared" si="10"/>
         <v>776.25</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="B16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
         <f>2/23</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="F16" s="1">
-        <f>0.8*E16*(C16+D16)/2</f>
+      <c r="G16" s="5">
+        <f t="shared" si="8"/>
         <v>6.9565217391304349E-2</v>
       </c>
-      <c r="G16" s="1">
-        <f>F16*0.5</f>
+      <c r="H16" s="5">
+        <f t="shared" si="7"/>
+        <v>120.20869565217392</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
         <v>3.4782608695652174E-2</v>
       </c>
-      <c r="H16" s="1">
-        <f>1/F16</f>
+      <c r="J16" s="5">
+        <f t="shared" si="1"/>
         <v>14.375</v>
       </c>
-      <c r="I16" s="1">
-        <f>1/G16</f>
+      <c r="K16" s="5">
+        <f t="shared" si="2"/>
         <v>28.75</v>
       </c>
-      <c r="J16" s="5">
-        <f>H16*1728</f>
+      <c r="L16" s="6">
+        <f t="shared" si="9"/>
         <v>24840</v>
       </c>
-      <c r="K16" s="5">
-        <f>I16*27</f>
+      <c r="M16" s="6">
+        <f t="shared" si="10"/>
         <v>776.25</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="B17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="5">
         <f>2/23</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="F17" s="1">
-        <f>0.8*E17*(C17+D17)/2</f>
+      <c r="G17" s="5">
+        <f t="shared" si="8"/>
         <v>6.9565217391304349E-2</v>
       </c>
-      <c r="G17" s="1">
-        <f>F17*0.5</f>
+      <c r="H17" s="5">
+        <f t="shared" si="7"/>
+        <v>120.20869565217392</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
         <v>3.4782608695652174E-2</v>
       </c>
-      <c r="H17" s="1">
-        <f>1/F17</f>
+      <c r="J17" s="5">
+        <f t="shared" si="1"/>
         <v>14.375</v>
       </c>
-      <c r="I17" s="1">
-        <f>1/G17</f>
+      <c r="K17" s="5">
+        <f t="shared" si="2"/>
         <v>28.75</v>
       </c>
-      <c r="J17" s="5">
-        <f>H17*1728</f>
+      <c r="L17" s="6">
+        <f t="shared" si="9"/>
         <v>24840</v>
       </c>
-      <c r="K17" s="5">
-        <f>I17*27</f>
+      <c r="M17" s="6">
+        <f t="shared" si="10"/>
         <v>776.25</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="B18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="5">
         <f>1/23</f>
         <v>4.3478260869565216E-2</v>
       </c>
-      <c r="F18" s="1">
-        <f>0.8*E18*(C18+D18)/2</f>
+      <c r="G18" s="5">
+        <f t="shared" si="8"/>
         <v>3.4782608695652174E-2</v>
       </c>
-      <c r="G18" s="1">
-        <f>F18*0.5</f>
+      <c r="H18" s="5">
+        <f t="shared" si="7"/>
+        <v>60.104347826086958</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
         <v>1.7391304347826087E-2</v>
       </c>
-      <c r="H18" s="1">
-        <f>1/F18</f>
+      <c r="J18" s="5">
+        <f t="shared" si="1"/>
         <v>28.75</v>
       </c>
-      <c r="I18" s="1">
-        <f>1/G18</f>
+      <c r="K18" s="5">
+        <f t="shared" si="2"/>
         <v>57.5</v>
       </c>
-      <c r="J18" s="5">
-        <f>H18*1728</f>
+      <c r="L18" s="6">
+        <f t="shared" si="9"/>
         <v>49680</v>
       </c>
-      <c r="K18" s="5">
-        <f>I18*27</f>
+      <c r="M18" s="6">
+        <f t="shared" si="10"/>
         <v>1552.5</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="B19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F19" s="5">
         <f>1/23</f>
         <v>4.3478260869565216E-2</v>
       </c>
-      <c r="F19" s="1">
-        <f>0.8*E19*(C19+D19)/2</f>
+      <c r="G19" s="5">
+        <f t="shared" si="8"/>
         <v>3.4782608695652174E-2</v>
       </c>
-      <c r="G19" s="1">
-        <f>F19*0.5</f>
+      <c r="H19" s="5">
+        <f t="shared" si="7"/>
+        <v>60.104347826086958</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
         <v>1.7391304347826087E-2</v>
       </c>
-      <c r="H19" s="1">
-        <f>1/F19</f>
+      <c r="J19" s="5">
+        <f t="shared" si="1"/>
         <v>28.75</v>
       </c>
-      <c r="I19" s="1">
-        <f>1/G19</f>
+      <c r="K19" s="5">
+        <f t="shared" si="2"/>
         <v>57.5</v>
       </c>
-      <c r="J19" s="5">
-        <f>H19*1728</f>
+      <c r="L19" s="6">
+        <f t="shared" si="9"/>
         <v>49680</v>
       </c>
-      <c r="K19" s="5">
-        <f>I19*27</f>
+      <c r="M19" s="6">
+        <f t="shared" si="10"/>
         <v>1552.5</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="B20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="5">
         <f>2/23</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="F20" s="1">
-        <f>0.8*E20*(C20+D20)/2</f>
+      <c r="G20" s="5">
+        <f t="shared" si="8"/>
         <v>6.9565217391304349E-2</v>
       </c>
-      <c r="G20" s="1">
-        <f>F20*0.5</f>
+      <c r="H20" s="5">
+        <f t="shared" si="7"/>
+        <v>120.20869565217392</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
         <v>3.4782608695652174E-2</v>
       </c>
-      <c r="H20" s="1">
-        <f>1/F20</f>
+      <c r="J20" s="5">
+        <f t="shared" si="1"/>
         <v>14.375</v>
       </c>
-      <c r="I20" s="1">
-        <f>1/G20</f>
+      <c r="K20" s="5">
+        <f t="shared" si="2"/>
         <v>28.75</v>
       </c>
-      <c r="J20" s="5">
-        <f>H20*1728</f>
+      <c r="L20" s="6">
+        <f t="shared" si="9"/>
         <v>24840</v>
       </c>
-      <c r="K20" s="5">
-        <f>I20*27</f>
+      <c r="M20" s="6">
+        <f t="shared" si="10"/>
         <v>776.25</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="5">
         <f>2/23</f>
         <v>8.6956521739130432E-2</v>
       </c>
-      <c r="F21" s="1">
-        <f>0.8*E21*(C21+D21)/2</f>
+      <c r="G21" s="5">
+        <f t="shared" si="8"/>
         <v>6.9565217391304349E-2</v>
       </c>
-      <c r="G21" s="1">
-        <f>F21*0.5</f>
+      <c r="H21" s="5">
+        <f t="shared" si="7"/>
+        <v>120.20869565217392</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
         <v>3.4782608695652174E-2</v>
       </c>
-      <c r="H21" s="1">
-        <f>1/F21</f>
+      <c r="J21" s="5">
+        <f t="shared" si="1"/>
         <v>14.375</v>
       </c>
-      <c r="I21" s="1">
-        <f>1/G21</f>
+      <c r="K21" s="5">
+        <f t="shared" si="2"/>
         <v>28.75</v>
       </c>
-      <c r="J21" s="5">
-        <f>H21*1728</f>
+      <c r="L21" s="6">
+        <f t="shared" si="9"/>
         <v>24840</v>
       </c>
-      <c r="K21" s="5">
-        <f>I21*27</f>
+      <c r="M21" s="6">
+        <f t="shared" si="10"/>
         <v>776.25</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1">
+        <v>17</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="5">
         <f>4/12</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F22" s="1">
-        <f>0.25*E22*(C22+D22)/2</f>
+      <c r="G22" s="5">
+        <f>0.25*F22*E22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G22" s="1">
-        <f>F22*0.5</f>
+      <c r="H22" s="5">
+        <f t="shared" si="7"/>
+        <v>144</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="H22" s="1">
-        <f>1/F22</f>
+      <c r="J22" s="5">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="I22" s="1">
-        <f>1/G22</f>
+      <c r="K22" s="5">
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="J22">
-        <f>H22*1728</f>
+      <c r="L22" s="5">
+        <f t="shared" si="9"/>
         <v>20736</v>
       </c>
-      <c r="K22">
-        <f>I22*1728</f>
+      <c r="M22" s="5">
+        <f>K22*1728</f>
         <v>41472</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1">
+        <v>33</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="5">
         <f>3/12</f>
         <v>0.25</v>
       </c>
-      <c r="F23" s="1">
-        <f>0.25*E23*(C23+D23)/2</f>
+      <c r="G23" s="5">
+        <f t="shared" ref="G23:G26" si="11">0.25*F23*E23</f>
         <v>6.25E-2</v>
       </c>
-      <c r="G23" s="1">
-        <f>F23*0.5</f>
+      <c r="H23" s="5">
+        <f t="shared" si="7"/>
+        <v>108</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
         <v>3.125E-2</v>
       </c>
-      <c r="H23" s="1">
-        <f>1/F23</f>
+      <c r="J23" s="5">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="I23" s="1">
-        <f>1/G23</f>
+      <c r="K23" s="5">
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="J23">
-        <f>H23*1728</f>
+      <c r="L23" s="5">
+        <f t="shared" si="9"/>
         <v>27648</v>
       </c>
-      <c r="K23">
-        <f>I23*1728</f>
+      <c r="M23" s="5">
+        <f>K23*1728</f>
         <v>55296</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="B24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="5">
         <f>2/12</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="F24" s="1">
-        <f>0.25*E24*(C24+D24)/2</f>
+      <c r="G24" s="5">
+        <f t="shared" si="11"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="G24" s="1">
-        <f>F24*0.5</f>
+      <c r="H24" s="5">
+        <f t="shared" si="7"/>
+        <v>72</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="0"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="H24" s="1">
-        <f>1/F24</f>
+      <c r="J24" s="5">
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="I24" s="1">
-        <f>1/G24</f>
+      <c r="K24" s="5">
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="J24" s="5">
-        <f>H24*1728</f>
+      <c r="L24" s="6">
+        <f t="shared" si="9"/>
         <v>41472</v>
       </c>
-      <c r="K24" s="5">
-        <f>I24*27</f>
+      <c r="M24" s="6">
+        <f>K24*27</f>
         <v>1296</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F25" s="5">
         <f>2/12</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="F25" s="1">
-        <f>0.25*E25*(C25+D25)/2</f>
+      <c r="G25" s="5">
+        <f t="shared" si="11"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="G25" s="1">
-        <f>F25*0.5</f>
+      <c r="H25" s="5">
+        <f t="shared" si="7"/>
+        <v>72</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="H25" s="1">
-        <f>1/F25</f>
+      <c r="J25" s="5">
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="I25" s="1">
-        <f>1/G25</f>
+      <c r="K25" s="5">
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="J25" s="5">
-        <f>H25*1728</f>
+      <c r="L25" s="6">
+        <f t="shared" si="9"/>
         <v>41472</v>
       </c>
-      <c r="K25" s="5">
-        <f>I25*27</f>
+      <c r="M25" s="6">
+        <f>K25*27</f>
         <v>1296</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="B26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F26" s="5">
         <f>1/12</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="F26" s="1">
-        <f>0.25*E26*(C26+D26)/2</f>
+      <c r="G26" s="5">
+        <f t="shared" si="11"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="G26" s="1">
-        <f>F26*0.5</f>
+      <c r="H26" s="5">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="H26" s="1">
-        <f>1/F26</f>
+      <c r="J26" s="5">
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="I26" s="1">
-        <f>1/G26</f>
+      <c r="K26" s="5">
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="J26">
-        <f>H26*1728</f>
+      <c r="L26" s="5">
+        <f t="shared" si="9"/>
         <v>82944</v>
       </c>
-      <c r="K26">
-        <f>I26*27</f>
+      <c r="M26" s="5">
+        <f>K26*27</f>
         <v>2592</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1">
+        <v>34</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F27" s="5">
         <f>1/15</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="F27" s="1">
-        <f>2.2*E27*(C27+D27)/2</f>
+      <c r="G27" s="5">
+        <f>2.2*F27*E27</f>
         <v>0.14666666666666667</v>
       </c>
-      <c r="G27" s="1">
-        <f>F27*0.3</f>
+      <c r="H27" s="5">
+        <f t="shared" si="7"/>
+        <v>253.44</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" ref="I27:I46" si="12">G27*0.3</f>
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="H27" s="1">
-        <f>1/F27</f>
+      <c r="J27" s="5">
+        <f t="shared" si="1"/>
         <v>6.8181818181818183</v>
       </c>
-      <c r="I27" s="1">
-        <f>1/G27</f>
+      <c r="K27" s="5">
+        <f t="shared" si="2"/>
         <v>22.72727272727273</v>
       </c>
-      <c r="J27">
-        <f>H27*1728</f>
+      <c r="L27" s="5">
+        <f t="shared" si="9"/>
         <v>11781.818181818182</v>
       </c>
-      <c r="K27">
-        <f>I27*1728</f>
+      <c r="M27" s="5">
+        <f>K27*1728</f>
         <v>39272.727272727279</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="C28" s="5">
         <v>4</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="5">
         <v>12</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="5">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="F28" s="5">
         <f>3/15</f>
         <v>0.2</v>
       </c>
-      <c r="F28" s="1">
-        <f>2.2*E28*(C28+D28)/2</f>
+      <c r="G28" s="5">
+        <f t="shared" ref="G28:G31" si="13">2.2*F28*E28</f>
         <v>3.5200000000000005</v>
       </c>
-      <c r="G28" s="1">
-        <f>F28*0.3</f>
+      <c r="H28" s="5">
+        <f t="shared" si="7"/>
+        <v>6082.56</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="12"/>
         <v>1.056</v>
       </c>
-      <c r="H28" s="1">
-        <f>1/F28</f>
+      <c r="J28" s="5">
+        <f t="shared" si="1"/>
         <v>0.28409090909090906</v>
       </c>
-      <c r="I28" s="1">
-        <f>1/G28</f>
+      <c r="K28" s="5">
+        <f t="shared" si="2"/>
         <v>0.94696969696969691</v>
       </c>
-      <c r="J28">
-        <f>H28*1728</f>
+      <c r="L28" s="5">
+        <f t="shared" si="9"/>
         <v>490.90909090909088</v>
       </c>
-      <c r="K28">
-        <f>I28*1728</f>
+      <c r="M28" s="5">
+        <f>K28*1728</f>
         <v>1636.3636363636363</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="4">
         <v>8</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="4">
         <v>12</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="5">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="F29" s="4">
         <f>4/15</f>
         <v>0.26666666666666666</v>
       </c>
-      <c r="F29" s="3">
-        <f>2.2*E29*(C29+D29)/2</f>
+      <c r="G29" s="5">
+        <f t="shared" si="13"/>
         <v>5.8666666666666671</v>
       </c>
-      <c r="G29" s="3">
-        <f>F29*0.3</f>
+      <c r="H29" s="5">
+        <f t="shared" si="7"/>
+        <v>10137.6</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="12"/>
         <v>1.76</v>
       </c>
-      <c r="H29" s="3">
-        <f>1/F29</f>
+      <c r="J29" s="4">
+        <f t="shared" si="1"/>
         <v>0.17045454545454544</v>
       </c>
-      <c r="I29" s="3">
-        <f>1/G29</f>
+      <c r="K29" s="4">
+        <f t="shared" si="2"/>
         <v>0.56818181818181823</v>
       </c>
-      <c r="J29">
-        <f>H29*1728</f>
+      <c r="L29" s="5">
+        <f t="shared" si="9"/>
         <v>294.5454545454545</v>
       </c>
-      <c r="K29">
-        <f>I29*1728</f>
+      <c r="M29" s="5">
+        <f>K29*1728</f>
         <v>981.81818181818187</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>3</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="5">
         <v>4</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="5">
         <v>10</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="5">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="F30" s="5">
         <f>5/15</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F30" s="1">
-        <f>2.2*E30*(C30+D30)/2</f>
+      <c r="G30" s="5">
+        <f t="shared" si="13"/>
         <v>5.1333333333333337</v>
       </c>
-      <c r="G30" s="1">
-        <f>F30*0.3</f>
+      <c r="H30" s="5">
+        <f t="shared" si="7"/>
+        <v>8870.4000000000015</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="12"/>
         <v>1.54</v>
       </c>
-      <c r="H30" s="1">
-        <f>1/F30</f>
+      <c r="J30" s="5">
+        <f t="shared" si="1"/>
         <v>0.19480519480519479</v>
       </c>
-      <c r="I30" s="1">
-        <f>1/G30</f>
+      <c r="K30" s="5">
+        <f t="shared" si="2"/>
         <v>0.64935064935064934</v>
       </c>
-      <c r="J30">
-        <f>H30*1728</f>
+      <c r="L30" s="5">
+        <f t="shared" si="9"/>
         <v>336.6233766233766</v>
       </c>
-      <c r="K30">
-        <f>I30*1728</f>
+      <c r="M30" s="5">
+        <f>K30*1728</f>
         <v>1122.077922077922</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="3">
+      <c r="B31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="4">
         <v>2</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="4">
         <v>3</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="5">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+      <c r="F31" s="4">
         <f>2/15</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="F31" s="3">
-        <f>2.2*E31*(C31+D31)/2</f>
+      <c r="G31" s="5">
+        <f t="shared" si="13"/>
         <v>0.73333333333333339</v>
       </c>
-      <c r="G31" s="3">
-        <f>F31*0.3</f>
+      <c r="H31" s="5">
+        <f t="shared" si="7"/>
+        <v>1267.2</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="12"/>
         <v>0.22</v>
       </c>
-      <c r="H31" s="3">
-        <f>1/F31</f>
+      <c r="J31" s="4">
+        <f t="shared" si="1"/>
         <v>1.3636363636363635</v>
       </c>
-      <c r="I31" s="3">
-        <f>1/G31</f>
+      <c r="K31" s="4">
+        <f t="shared" si="2"/>
         <v>4.5454545454545459</v>
       </c>
-      <c r="J31">
-        <f>H31*1728</f>
+      <c r="L31" s="5">
+        <f t="shared" si="9"/>
         <v>2356.363636363636</v>
       </c>
-      <c r="K31">
-        <f>I31*1728</f>
+      <c r="M31" s="5">
+        <f>K31*1728</f>
         <v>7854.545454545455</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="1">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="B32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="5">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F32" s="5">
         <f>4/29</f>
         <v>0.13793103448275862</v>
       </c>
-      <c r="F32" s="1">
-        <f>0.8*E32*(C32+D32)/2</f>
+      <c r="G32" s="5">
+        <f>0.8*F32*E32</f>
         <v>0.1103448275862069</v>
       </c>
-      <c r="G32" s="1">
-        <f>F32*0.3</f>
+      <c r="H32" s="5">
+        <f t="shared" si="7"/>
+        <v>190.6758620689655</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="12"/>
         <v>3.310344827586207E-2</v>
       </c>
-      <c r="H32" s="1">
-        <f>1/F32</f>
+      <c r="J32" s="5">
+        <f t="shared" si="1"/>
         <v>9.0625</v>
       </c>
-      <c r="I32" s="1">
-        <f>1/G32</f>
+      <c r="K32" s="5">
+        <f t="shared" si="2"/>
         <v>30.208333333333332</v>
       </c>
-      <c r="J32" s="5">
-        <f>H32*1728</f>
+      <c r="L32" s="6">
+        <f t="shared" si="9"/>
         <v>15660</v>
       </c>
-      <c r="K32" s="5">
-        <f>I32*27</f>
+      <c r="M32" s="6">
+        <f t="shared" ref="M32:M37" si="14">K32*27</f>
         <v>815.625</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F33" s="5">
         <f>2/29</f>
         <v>6.8965517241379309E-2</v>
       </c>
-      <c r="F33" s="1">
-        <f>0.8*E33*(C33+D33)/2</f>
+      <c r="G33" s="5">
+        <f t="shared" ref="G33:G41" si="15">0.8*F33*E33</f>
         <v>5.5172413793103448E-2</v>
       </c>
-      <c r="G33" s="1">
-        <f>F33*0.3</f>
+      <c r="H33" s="5">
+        <f t="shared" si="7"/>
+        <v>95.33793103448275</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="12"/>
         <v>1.6551724137931035E-2</v>
       </c>
-      <c r="H33" s="1">
-        <f>1/F33</f>
+      <c r="J33" s="5">
+        <f t="shared" si="1"/>
         <v>18.125</v>
       </c>
-      <c r="I33" s="1">
-        <f>1/G33</f>
+      <c r="K33" s="5">
+        <f t="shared" si="2"/>
         <v>60.416666666666664</v>
       </c>
-      <c r="J33" s="5">
-        <f>H33*1728</f>
+      <c r="L33" s="6">
+        <f t="shared" si="9"/>
         <v>31320</v>
       </c>
-      <c r="K33" s="5">
-        <f>I33*27</f>
+      <c r="M33" s="6">
+        <f t="shared" si="14"/>
         <v>1631.25</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="B34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="5">
         <f>2/29</f>
         <v>6.8965517241379309E-2</v>
       </c>
-      <c r="F34" s="1">
-        <f>0.8*E34*(C34+D34)/2</f>
+      <c r="G34" s="5">
+        <f t="shared" si="15"/>
         <v>5.5172413793103448E-2</v>
       </c>
-      <c r="G34" s="1">
-        <f>F34*0.3</f>
+      <c r="H34" s="5">
+        <f t="shared" si="7"/>
+        <v>95.33793103448275</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="12"/>
         <v>1.6551724137931035E-2</v>
       </c>
-      <c r="H34" s="1">
-        <f>1/F34</f>
+      <c r="J34" s="5">
+        <f t="shared" si="1"/>
         <v>18.125</v>
       </c>
-      <c r="I34" s="1">
-        <f>1/G34</f>
+      <c r="K34" s="5">
+        <f t="shared" si="2"/>
         <v>60.416666666666664</v>
       </c>
-      <c r="J34" s="5">
-        <f>H34*1728</f>
+      <c r="L34" s="6">
+        <f t="shared" si="9"/>
         <v>31320</v>
       </c>
-      <c r="K34" s="5">
-        <f>I34*27</f>
+      <c r="M34" s="6">
+        <f t="shared" si="14"/>
         <v>1631.25</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1</v>
-      </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="B35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="5">
         <f>2/29</f>
         <v>6.8965517241379309E-2</v>
       </c>
-      <c r="F35" s="1">
-        <f>0.8*E35*(C35+D35)/2</f>
+      <c r="G35" s="5">
+        <f t="shared" si="15"/>
         <v>5.5172413793103448E-2</v>
       </c>
-      <c r="G35" s="1">
-        <f>F35*0.3</f>
+      <c r="H35" s="5">
+        <f t="shared" si="7"/>
+        <v>95.33793103448275</v>
+      </c>
+      <c r="I35" s="5">
+        <f t="shared" si="12"/>
         <v>1.6551724137931035E-2</v>
       </c>
-      <c r="H35" s="1">
-        <f>1/F35</f>
+      <c r="J35" s="5">
+        <f t="shared" si="1"/>
         <v>18.125</v>
       </c>
-      <c r="I35" s="1">
-        <f>1/G35</f>
+      <c r="K35" s="5">
+        <f t="shared" si="2"/>
         <v>60.416666666666664</v>
       </c>
-      <c r="J35" s="5">
-        <f>H35*1728</f>
+      <c r="L35" s="6">
+        <f t="shared" si="9"/>
         <v>31320</v>
       </c>
-      <c r="K35" s="5">
-        <f>I35*27</f>
+      <c r="M35" s="6">
+        <f t="shared" si="14"/>
         <v>1631.25</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="B36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F36" s="5">
         <f>3/29</f>
         <v>0.10344827586206896</v>
       </c>
-      <c r="F36" s="1">
-        <f>0.8*E36*(C36+D36)/2</f>
+      <c r="G36" s="5">
+        <f t="shared" si="15"/>
         <v>8.2758620689655171E-2</v>
       </c>
-      <c r="G36" s="1">
-        <f>F36*0.3</f>
+      <c r="H36" s="5">
+        <f t="shared" si="7"/>
+        <v>143.00689655172414</v>
+      </c>
+      <c r="I36" s="5">
+        <f t="shared" si="12"/>
         <v>2.4827586206896551E-2</v>
       </c>
-      <c r="H36" s="1">
-        <f>1/F36</f>
+      <c r="J36" s="5">
+        <f t="shared" si="1"/>
         <v>12.083333333333334</v>
       </c>
-      <c r="I36" s="1">
-        <f>1/G36</f>
+      <c r="K36" s="5">
+        <f t="shared" si="2"/>
         <v>40.277777777777779</v>
       </c>
-      <c r="J36" s="5">
-        <f>H36*1728</f>
+      <c r="L36" s="6">
+        <f t="shared" si="9"/>
         <v>20880</v>
       </c>
-      <c r="K36" s="5">
-        <f>I36*27</f>
+      <c r="M36" s="6">
+        <f t="shared" si="14"/>
         <v>1087.5</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="B37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F37" s="5">
         <f>3/29</f>
         <v>0.10344827586206896</v>
       </c>
-      <c r="F37" s="1">
-        <f>0.8*E37*(C37+D37)/2</f>
+      <c r="G37" s="5">
+        <f t="shared" si="15"/>
         <v>8.2758620689655171E-2</v>
       </c>
-      <c r="G37" s="1">
-        <f>F37*0.3</f>
+      <c r="H37" s="5">
+        <f t="shared" si="7"/>
+        <v>143.00689655172414</v>
+      </c>
+      <c r="I37" s="5">
+        <f t="shared" si="12"/>
         <v>2.4827586206896551E-2</v>
       </c>
-      <c r="H37" s="1">
-        <f>1/F37</f>
+      <c r="J37" s="5">
+        <f t="shared" si="1"/>
         <v>12.083333333333334</v>
       </c>
-      <c r="I37" s="1">
-        <f>1/G37</f>
+      <c r="K37" s="5">
+        <f t="shared" si="2"/>
         <v>40.277777777777779</v>
       </c>
-      <c r="J37" s="5">
-        <f>H37*1728</f>
+      <c r="L37" s="6">
+        <f t="shared" si="9"/>
         <v>20880</v>
       </c>
-      <c r="K37" s="5">
-        <f>I37*27</f>
+      <c r="M37" s="6">
+        <f t="shared" si="14"/>
         <v>1087.5</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
+        <v>17</v>
+      </c>
+      <c r="C38" s="5">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F38" s="5">
         <f>3/29</f>
         <v>0.10344827586206896</v>
       </c>
-      <c r="F38" s="1">
-        <f>0.8*E38*(C38+D38)/2</f>
+      <c r="G38" s="5">
+        <f t="shared" si="15"/>
         <v>8.2758620689655171E-2</v>
       </c>
-      <c r="G38" s="1">
-        <f>F38*0.3</f>
+      <c r="H38" s="5">
+        <f t="shared" si="7"/>
+        <v>143.00689655172414</v>
+      </c>
+      <c r="I38" s="5">
+        <f t="shared" si="12"/>
         <v>2.4827586206896551E-2</v>
       </c>
-      <c r="H38" s="1">
-        <f>1/F38</f>
+      <c r="J38" s="5">
+        <f t="shared" si="1"/>
         <v>12.083333333333334</v>
       </c>
-      <c r="I38" s="1">
-        <f>1/G38</f>
+      <c r="K38" s="5">
+        <f t="shared" si="2"/>
         <v>40.277777777777779</v>
       </c>
-      <c r="J38">
-        <f>H38*1728</f>
+      <c r="L38" s="5">
+        <f t="shared" si="9"/>
         <v>20880</v>
       </c>
-      <c r="K38">
-        <f>I38*1728</f>
+      <c r="M38" s="5">
+        <f t="shared" ref="M38:M43" si="16">K38*1728</f>
         <v>69600</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
+        <v>20</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F39" s="5">
         <f>5/29</f>
         <v>0.17241379310344829</v>
       </c>
-      <c r="F39" s="1">
-        <f>0.8*E39*(C39+D39)/2</f>
+      <c r="G39" s="5">
+        <f t="shared" si="15"/>
         <v>0.13793103448275865</v>
       </c>
-      <c r="G39" s="1">
-        <f>F39*0.3</f>
+      <c r="H39" s="5">
+        <f t="shared" si="7"/>
+        <v>238.34482758620695</v>
+      </c>
+      <c r="I39" s="5">
+        <f t="shared" si="12"/>
         <v>4.1379310344827593E-2</v>
       </c>
-      <c r="H39" s="1">
-        <f>1/F39</f>
+      <c r="J39" s="5">
+        <f t="shared" si="1"/>
         <v>7.2499999999999982</v>
       </c>
-      <c r="I39" s="1">
-        <f>1/G39</f>
+      <c r="K39" s="5">
+        <f t="shared" si="2"/>
         <v>24.166666666666664</v>
       </c>
-      <c r="J39">
-        <f>H39*1728</f>
+      <c r="L39" s="5">
+        <f t="shared" si="9"/>
         <v>12527.999999999996</v>
       </c>
-      <c r="K39">
-        <f>I39*1728</f>
+      <c r="M39" s="5">
+        <f t="shared" si="16"/>
         <v>41759.999999999993</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
+        <v>21</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="5">
         <f>4/29</f>
         <v>0.13793103448275862</v>
       </c>
-      <c r="F40" s="1">
-        <f>0.8*E40*(C40+D40)/2</f>
+      <c r="G40" s="5">
+        <f t="shared" si="15"/>
         <v>0.1103448275862069</v>
       </c>
-      <c r="G40" s="1">
-        <f>F40*0.3</f>
+      <c r="H40" s="5">
+        <f t="shared" si="7"/>
+        <v>190.6758620689655</v>
+      </c>
+      <c r="I40" s="5">
+        <f t="shared" si="12"/>
         <v>3.310344827586207E-2</v>
       </c>
-      <c r="H40" s="1">
-        <f>1/F40</f>
+      <c r="J40" s="5">
+        <f t="shared" si="1"/>
         <v>9.0625</v>
       </c>
-      <c r="I40" s="1">
-        <f>1/G40</f>
+      <c r="K40" s="5">
+        <f t="shared" si="2"/>
         <v>30.208333333333332</v>
       </c>
-      <c r="J40">
-        <f>H40*1728</f>
+      <c r="L40" s="5">
+        <f t="shared" si="9"/>
         <v>15660</v>
       </c>
-      <c r="K40">
-        <f>I40*1728</f>
+      <c r="M40" s="5">
+        <f t="shared" si="16"/>
         <v>52200</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="3">
-        <v>1</v>
-      </c>
-      <c r="D41" s="3">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="B41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="4">
+        <v>1</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
         <f>1/29</f>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="F41" s="3">
-        <f>0.8*E41*(C41+D41)/2</f>
+      <c r="G41" s="5">
+        <f t="shared" si="15"/>
         <v>2.7586206896551724E-2</v>
       </c>
-      <c r="G41" s="3">
-        <f>F41*0.3</f>
+      <c r="H41" s="5">
+        <f t="shared" si="7"/>
+        <v>47.668965517241375</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="12"/>
         <v>8.2758620689655175E-3</v>
       </c>
-      <c r="H41" s="3">
-        <f>1/F41</f>
+      <c r="J41" s="4">
+        <f t="shared" si="1"/>
         <v>36.25</v>
       </c>
-      <c r="I41" s="3">
-        <f>1/G41</f>
+      <c r="K41" s="4">
+        <f t="shared" si="2"/>
         <v>120.83333333333333</v>
       </c>
-      <c r="J41">
-        <f>H41*1728</f>
+      <c r="L41" s="5">
+        <f t="shared" si="9"/>
         <v>62640</v>
       </c>
-      <c r="K41">
-        <f>I41*1728</f>
+      <c r="M41" s="5">
+        <f t="shared" si="16"/>
         <v>208800</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="3">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3">
+      <c r="B42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="4">
+        <v>1</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
         <f>3/10</f>
         <v>0.3</v>
       </c>
-      <c r="F42" s="3">
-        <f>0.75*E42*(C42+D42)/2</f>
+      <c r="G42" s="4">
+        <f>0.75*F42*E42</f>
         <v>0.22499999999999998</v>
       </c>
-      <c r="G42" s="3">
-        <f>F42*0.3</f>
+      <c r="H42" s="5">
+        <f t="shared" si="7"/>
+        <v>388.79999999999995</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="12"/>
         <v>6.7499999999999991E-2</v>
       </c>
-      <c r="H42" s="3">
-        <f>1/F42</f>
+      <c r="J42" s="4">
+        <f t="shared" si="1"/>
         <v>4.4444444444444446</v>
       </c>
-      <c r="I42" s="3">
-        <f>1/G42</f>
+      <c r="K42" s="4">
+        <f t="shared" si="2"/>
         <v>14.814814814814817</v>
       </c>
-      <c r="J42">
-        <f>H42*1728</f>
+      <c r="L42" s="5">
+        <f t="shared" si="9"/>
         <v>7680</v>
       </c>
-      <c r="K42">
-        <f>I42*1728</f>
+      <c r="M42" s="5">
+        <f t="shared" si="16"/>
         <v>25600.000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1">
+        <v>28</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F43" s="5">
         <f>3/10</f>
         <v>0.3</v>
       </c>
-      <c r="F43" s="1">
-        <f>0.75*E43*(C43+D43)/2</f>
+      <c r="G43" s="4">
+        <f t="shared" ref="G43:G46" si="17">0.75*F43*E43</f>
         <v>0.22499999999999998</v>
       </c>
-      <c r="G43" s="1">
-        <f>F43*0.3</f>
+      <c r="H43" s="5">
+        <f t="shared" si="7"/>
+        <v>388.79999999999995</v>
+      </c>
+      <c r="I43" s="5">
+        <f t="shared" si="12"/>
         <v>6.7499999999999991E-2</v>
       </c>
-      <c r="H43" s="1">
-        <f>1/F43</f>
+      <c r="J43" s="5">
+        <f t="shared" si="1"/>
         <v>4.4444444444444446</v>
       </c>
-      <c r="I43" s="1">
-        <f>1/G43</f>
+      <c r="K43" s="5">
+        <f t="shared" si="2"/>
         <v>14.814814814814817</v>
       </c>
-      <c r="J43">
-        <f>H43*1728</f>
+      <c r="L43" s="5">
+        <f t="shared" si="9"/>
         <v>7680</v>
       </c>
-      <c r="K43">
-        <f>I43*1728</f>
+      <c r="M43" s="5">
+        <f t="shared" si="16"/>
         <v>25600.000000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="1">
-        <v>1</v>
-      </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="B44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F44" s="5">
         <f>2/10</f>
         <v>0.2</v>
       </c>
-      <c r="F44" s="1">
-        <f>0.75*E44*(C44+D44)/2</f>
+      <c r="G44" s="4">
+        <f t="shared" si="17"/>
         <v>0.15000000000000002</v>
       </c>
-      <c r="G44" s="1">
-        <f>F44*0.3</f>
+      <c r="H44" s="5">
+        <f t="shared" si="7"/>
+        <v>259.20000000000005</v>
+      </c>
+      <c r="I44" s="5">
+        <f t="shared" si="12"/>
         <v>4.5000000000000005E-2</v>
       </c>
-      <c r="H44" s="1">
-        <f>1/F44</f>
+      <c r="J44" s="5">
+        <f t="shared" si="1"/>
         <v>6.6666666666666661</v>
       </c>
-      <c r="I44" s="1">
-        <f>1/G44</f>
+      <c r="K44" s="5">
+        <f t="shared" si="2"/>
         <v>22.222222222222218</v>
       </c>
-      <c r="J44" s="5">
-        <f>H44*1728</f>
+      <c r="L44" s="6">
+        <f t="shared" si="9"/>
         <v>11519.999999999998</v>
       </c>
-      <c r="K44" s="5">
-        <f>I44*27</f>
+      <c r="M44" s="6">
+        <f>K44*27</f>
         <v>599.99999999999989</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="B45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F45" s="5">
         <f>1/10</f>
         <v>0.1</v>
       </c>
-      <c r="F45" s="1">
-        <f>0.75*E45*(C45+D45)/2</f>
+      <c r="G45" s="4">
+        <f t="shared" si="17"/>
         <v>7.5000000000000011E-2</v>
       </c>
-      <c r="G45" s="1">
-        <f>F45*0.3</f>
+      <c r="H45" s="5">
+        <f t="shared" si="7"/>
+        <v>129.60000000000002</v>
+      </c>
+      <c r="I45" s="5">
+        <f t="shared" si="12"/>
         <v>2.2500000000000003E-2</v>
       </c>
-      <c r="H45" s="1">
-        <f>1/F45</f>
+      <c r="J45" s="5">
+        <f t="shared" si="1"/>
         <v>13.333333333333332</v>
       </c>
-      <c r="I45" s="1">
-        <f>1/G45</f>
+      <c r="K45" s="5">
+        <f t="shared" si="2"/>
         <v>44.444444444444436</v>
       </c>
-      <c r="J45" s="5">
-        <f>H45*1728</f>
+      <c r="L45" s="6">
+        <f t="shared" si="9"/>
         <v>23039.999999999996</v>
       </c>
-      <c r="K45" s="5">
-        <f>I45*27</f>
+      <c r="M45" s="6">
+        <f>K45*27</f>
         <v>1199.9999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="3">
-        <v>1</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="B46" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="F46" s="4">
         <f>1/10</f>
         <v>0.1</v>
       </c>
-      <c r="F46" s="3">
-        <f>0.75*E46*(C46+D46)/2</f>
+      <c r="G46" s="4">
+        <f t="shared" si="17"/>
         <v>7.5000000000000011E-2</v>
       </c>
-      <c r="G46" s="3">
-        <f>F46*0.3</f>
+      <c r="H46" s="5">
+        <f t="shared" si="7"/>
+        <v>129.60000000000002</v>
+      </c>
+      <c r="I46" s="4">
+        <f t="shared" si="12"/>
         <v>2.2500000000000003E-2</v>
       </c>
-      <c r="H46" s="3">
-        <f>1/F46</f>
+      <c r="J46" s="4">
+        <f t="shared" si="1"/>
         <v>13.333333333333332</v>
       </c>
-      <c r="I46" s="3">
-        <f>1/G46</f>
+      <c r="K46" s="4">
+        <f t="shared" si="2"/>
         <v>44.444444444444436</v>
       </c>
-      <c r="J46">
-        <f>H46*1728</f>
+      <c r="L46" s="5">
+        <f t="shared" si="9"/>
         <v>23039.999999999996</v>
       </c>
-      <c r="K46">
-        <f>I46*1728</f>
+      <c r="M46" s="5">
+        <f>K46*1728</f>
         <v>76799.999999999985</v>
       </c>
     </row>
